--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Recoletas Salud San Pablo Burgos.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Recoletas Salud San Pablo Burgos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2294.16</v>
+        <v>2611.88</v>
       </c>
       <c r="C2" t="n">
-        <v>2288.04</v>
+        <v>2601.12</v>
       </c>
       <c r="D2" t="n">
-        <v>109.3949406478908</v>
+        <v>109.9526357876607</v>
       </c>
       <c r="E2" t="n">
-        <v>113.8966101991224</v>
+        <v>113.8355785200222</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5135967162647511</v>
+        <v>0.5143820224719101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.147606503769643</v>
+        <v>0.1460470810544666</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3207373271889401</v>
+        <v>0.317741935483871</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2570548999486916</v>
+        <v>0.256629213483146</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="M2" t="n">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="N2" t="n">
-        <v>960</v>
+        <v>1093</v>
       </c>
       <c r="O2" t="n">
-        <v>1333</v>
+        <v>1508</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6839404822986147</v>
+        <v>0.677752808988764</v>
       </c>
       <c r="Q2" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="R2" t="n">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1980502821959979</v>
+        <v>0.1973033707865169</v>
       </c>
       <c r="T2" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="U2" t="n">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1195484864032837</v>
+        <v>0.117752808988764</v>
       </c>
       <c r="W2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="X2" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0836326321190354</v>
+        <v>0.08134831460674158</v>
       </c>
       <c r="Z2" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="AA2" t="n">
-        <v>523</v>
+        <v>612</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2683427398665982</v>
+        <v>0.2750561797752809</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7201800450112528</v>
+        <v>0.7248010610079576</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3989637305699482</v>
+        <v>0.3826879271070615</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3004291845493562</v>
+        <v>0.3091603053435115</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2883435582822086</v>
+        <v>0.281767955801105</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3154875717017208</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.440360090022506</v>
+        <v>1.449602122015915</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6008583690987125</v>
+        <v>0.6183206106870229</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9271137026239067</v>
+        <v>0.9419924337957125</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8634361233480177</v>
+        <v>0.857976653696498</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9281609195402298</v>
+        <v>0.949238578680203</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.683168316831683</v>
+        <v>1.655172413793103</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.284615384615385</v>
+        <v>1.291571753986333</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.997435897435897</v>
+        <v>5.068337129840547</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.282051282051282</v>
+        <v>6.359908883826879</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.93428571428571</v>
+        <v>81.62124999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>81.71571428571428</v>
+        <v>81.285</v>
       </c>
       <c r="D3" t="n">
-        <v>109.3949406478908</v>
+        <v>109.9526357876607</v>
       </c>
       <c r="E3" t="n">
-        <v>113.8966101991224</v>
+        <v>113.8355785200222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5135967162647511</v>
+        <v>0.5143820224719101</v>
       </c>
       <c r="G3" t="n">
-        <v>0.147606503769643</v>
+        <v>0.1460470810544666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3207373271889401</v>
+        <v>0.317741935483871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2570548999486916</v>
+        <v>0.256629213483146</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>13.78125</v>
       </c>
       <c r="K3" t="n">
-        <v>11.53571428571429</v>
+        <v>11.6875</v>
       </c>
       <c r="L3" t="n">
-        <v>6.071428571428571</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>12.78571428571429</v>
+        <v>12.65625</v>
       </c>
       <c r="N3" t="n">
-        <v>34.28571428571428</v>
+        <v>34.15625</v>
       </c>
       <c r="O3" t="n">
-        <v>47.60714285714285</v>
+        <v>47.125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6839404822986146</v>
+        <v>0.677752808988764</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>13.78571428571429</v>
+        <v>13.71875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1980502821959979</v>
+        <v>0.1973033707865169</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.53125</v>
       </c>
       <c r="U3" t="n">
-        <v>8.321428571428571</v>
+        <v>8.1875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1195484864032837</v>
+        <v>0.117752808988764</v>
       </c>
       <c r="W3" t="n">
-        <v>1.678571428571429</v>
+        <v>1.59375</v>
       </c>
       <c r="X3" t="n">
-        <v>5.821428571428571</v>
+        <v>5.65625</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08363263211903539</v>
+        <v>0.08134831460674158</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.892857142857143</v>
+        <v>6.1875</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.67857142857143</v>
+        <v>19.125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2683427398665982</v>
+        <v>0.2750561797752809</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7201800450112529</v>
+        <v>0.7248010610079576</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3989637305699482</v>
+        <v>0.3826879271070615</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3004291845493562</v>
+        <v>0.3091603053435115</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2883435582822086</v>
+        <v>0.281767955801105</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3154875717017209</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.440360090022506</v>
+        <v>1.449602122015915</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6008583690987125</v>
+        <v>0.6183206106870229</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9271137026239068</v>
+        <v>0.9419924337957125</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8634361233480176</v>
+        <v>0.857976653696498</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9281609195402299</v>
+        <v>0.949238578680203</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.683168316831683</v>
+        <v>1.655172413793103</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.284615384615384</v>
+        <v>1.291571753986333</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.997435897435897</v>
+        <v>5.068337129840547</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.282051282051282</v>
+        <v>6.359908883826879</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2281.92</v>
+        <v>2590.36</v>
       </c>
       <c r="C4" t="n">
-        <v>2288.04</v>
+        <v>2601.12</v>
       </c>
       <c r="D4" t="n">
-        <v>113.8966101991224</v>
+        <v>113.8355785200222</v>
       </c>
       <c r="E4" t="n">
-        <v>109.3949406478908</v>
+        <v>109.9526357876607</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5624303232998885</v>
+        <v>0.5614077669902913</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1755661428041084</v>
+        <v>0.1745117744520194</v>
       </c>
       <c r="H4" t="n">
-        <v>0.316008316008316</v>
+        <v>0.3212669683257919</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3277591973244147</v>
+        <v>0.3145631067961165</v>
       </c>
       <c r="J4" t="n">
+        <v>353</v>
+      </c>
+      <c r="K4" t="n">
+        <v>357</v>
+      </c>
+      <c r="L4" t="n">
+        <v>209</v>
+      </c>
+      <c r="M4" t="n">
+        <v>495</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1072</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1408</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6834951456310679</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>142</v>
+      </c>
+      <c r="R4" t="n">
         <v>316</v>
       </c>
-      <c r="K4" t="n">
-        <v>305</v>
-      </c>
-      <c r="L4" t="n">
-        <v>188</v>
-      </c>
-      <c r="M4" t="n">
-        <v>437</v>
-      </c>
-      <c r="N4" t="n">
-        <v>956</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1261</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.7028985507246377</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>124</v>
-      </c>
-      <c r="R4" t="n">
-        <v>278</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.1549609810479376</v>
+        <v>0.1533980582524272</v>
       </c>
       <c r="T4" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="U4" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1137123745819398</v>
+        <v>0.1135922330097087</v>
       </c>
       <c r="W4" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="X4" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1098104793756968</v>
+        <v>0.1077669902912621</v>
       </c>
       <c r="Z4" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="AA4" t="n">
-        <v>622</v>
+        <v>724</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.346711259754738</v>
+        <v>0.3514563106796116</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7581284694686756</v>
+        <v>0.7613636363636364</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4460431654676259</v>
+        <v>0.4493670886075949</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3725490196078431</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4822335025380711</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.319935691318328</v>
+        <v>0.319060773480663</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.516256938937351</v>
+        <v>1.522727272727273</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.076923076923077</v>
+        <v>1.056025369978858</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8102564102564103</v>
+        <v>0.8041002277904328</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.003289473684211</v>
+        <v>1.005633802816901</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.553719008264463</v>
+        <v>1.559701492537313</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.18942731277533</v>
+        <v>1.186770428015564</v>
       </c>
       <c r="AO4" t="n">
-        <v>3.951541850220264</v>
+        <v>4.007782101167315</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.140969162995595</v>
+        <v>5.19455252918288</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.49714285714286</v>
+        <v>80.94875</v>
       </c>
       <c r="C5" t="n">
-        <v>81.71571428571428</v>
+        <v>81.285</v>
       </c>
       <c r="D5" t="n">
-        <v>113.8966101991224</v>
+        <v>113.8355785200222</v>
       </c>
       <c r="E5" t="n">
-        <v>109.3949406478908</v>
+        <v>109.9526357876607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5624303232998885</v>
+        <v>0.5614077669902913</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1755661428041084</v>
+        <v>0.1745117744520194</v>
       </c>
       <c r="H5" t="n">
-        <v>0.316008316008316</v>
+        <v>0.3212669683257919</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3277591973244147</v>
+        <v>0.3145631067961165</v>
       </c>
       <c r="J5" t="n">
-        <v>11.28571428571429</v>
+        <v>11.03125</v>
       </c>
       <c r="K5" t="n">
-        <v>10.89285714285714</v>
+        <v>11.15625</v>
       </c>
       <c r="L5" t="n">
-        <v>6.714285714285714</v>
+        <v>6.53125</v>
       </c>
       <c r="M5" t="n">
-        <v>15.60714285714286</v>
+        <v>15.46875</v>
       </c>
       <c r="N5" t="n">
-        <v>34.14285714285715</v>
+        <v>33.5</v>
       </c>
       <c r="O5" t="n">
-        <v>45.03571428571428</v>
+        <v>44</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.6834951456310679</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.428571428571429</v>
+        <v>4.4375</v>
       </c>
       <c r="R5" t="n">
-        <v>9.928571428571429</v>
+        <v>9.875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1549609810479376</v>
+        <v>0.1533980582524272</v>
       </c>
       <c r="T5" t="n">
-        <v>2.714285714285714</v>
+        <v>2.84375</v>
       </c>
       <c r="U5" t="n">
-        <v>7.285714285714286</v>
+        <v>7.3125</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1137123745819398</v>
+        <v>0.1135922330097087</v>
       </c>
       <c r="W5" t="n">
-        <v>3.392857142857143</v>
+        <v>3.1875</v>
       </c>
       <c r="X5" t="n">
-        <v>7.035714285714286</v>
+        <v>6.9375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1098104793756968</v>
+        <v>0.1077669902912621</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.107142857142857</v>
+        <v>7.21875</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.21428571428572</v>
+        <v>22.625</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.346711259754738</v>
+        <v>0.3514563106796116</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7581284694686757</v>
+        <v>0.7613636363636364</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4460431654676259</v>
+        <v>0.4493670886075949</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3725490196078431</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4822335025380711</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3199356913183279</v>
+        <v>0.319060773480663</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.516256938937351</v>
+        <v>1.522727272727273</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.076923076923077</v>
+        <v>1.056025369978858</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8102564102564103</v>
+        <v>0.8041002277904328</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.00328947368421</v>
+        <v>1.005633802816901</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.553719008264463</v>
+        <v>1.559701492537313</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.18942731277533</v>
+        <v>1.186770428015564</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.951541850220264</v>
+        <v>4.007782101167315</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.140969162995595</v>
+        <v>5.19455252918288</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I8" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
+        <v>87</v>
+      </c>
+      <c r="L8" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>54</v>
+      </c>
+      <c r="R8" t="n">
+        <v>79</v>
+      </c>
+      <c r="S8" t="n">
         <v>75</v>
       </c>
-      <c r="L8" t="n">
-        <v>34</v>
-      </c>
-      <c r="M8" t="n">
-        <v>30</v>
-      </c>
-      <c r="N8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>47</v>
-      </c>
-      <c r="R8" t="n">
-        <v>70</v>
-      </c>
-      <c r="S8" t="n">
-        <v>64</v>
-      </c>
       <c r="T8" t="n">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="U8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="V8" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="W8" t="n">
         <v>29</v>
@@ -1488,81 +1488,81 @@
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="Z8" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.733</v>
+        <v>0.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.487</v>
+        <v>0.478</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.368</v>
+        <v>0.356</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>589:24</t>
+          <t>680:03</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>273.44</v>
+        <v>309.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.635</v>
+        <v>0.612</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.643</v>
+        <v>0.63</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.064</v>
+        <v>1.041</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.172</v>
+        <v>0.175</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.238</v>
+        <v>0.252</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.681</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.198</v>
+        <v>0.194</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AX8" t="n">
         <v>0.149</v>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.281</v>
+        <v>0.282</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.771</v>
+        <v>0.767</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1755,25 +1755,25 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="U10" t="n">
         <v>6</v>
@@ -1806,22 +1806,22 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="AB10" t="n">
         <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.615</v>
+        <v>0.571</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1852,26 +1852,26 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>173:47</t>
+          <t>193:39</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>61.48</v>
+        <v>68.36</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.596</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.615</v>
+        <v>0.587</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.09</v>
+        <v>1.053</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.234</v>
+        <v>0.226</v>
       </c>
       <c r="AU10" t="n">
         <v>0.714</v>
@@ -1880,13 +1880,13 @@
         <v>0.151</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.121</v>
+        <v>0.138</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="11">
@@ -2055,31 +2055,31 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>16</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -2088,31 +2088,31 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2124,19 +2124,19 @@
         <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2151,60 +2151,60 @@
         <v>0.333</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>48:29</t>
+          <t>72:47</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>22.4</v>
+        <v>37.28</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.265</v>
+        <v>0.293</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.374</v>
+        <v>0.365</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.714</v>
+        <v>0.671</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.045</v>
+        <v>0.08</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.412</v>
+        <v>0.276</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.197</v>
+        <v>0.219</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.121</v>
+        <v>0.08</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D13" t="n">
         <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K13" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
@@ -2256,19 +2256,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="S13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T13" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -2277,28 +2277,28 @@
         <v>13</v>
       </c>
       <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="n">
         <v>10</v>
       </c>
-      <c r="X13" t="n">
-        <v>8</v>
-      </c>
       <c r="Y13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="AB13" t="n">
         <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2322,48 +2322,48 @@
         <v>14</v>
       </c>
       <c r="AL13" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.298</v>
+        <v>0.269</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>527:06</t>
+          <t>584:24</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>173.24</v>
+        <v>184.12</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.415</v>
+        <v>0.392</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.481</v>
+        <v>0.462</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.768</v>
+        <v>0.733</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.202</v>
+        <v>0.206</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.297</v>
+        <v>0.296</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.429</v>
+        <v>2.395</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.091</v>
+        <v>0.098</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.099</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="14">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
         <v>8</v>
@@ -2424,16 +2424,16 @@
         <v>31</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="U14" t="n">
         <v>9</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>3</v>
@@ -2442,13 +2442,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8</v>
+        <v>0.769</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
@@ -2478,51 +2478,51 @@
         <v>0.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.35</v>
+        <v>0.364</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>202:45</t>
+          <t>221:30</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>47.88</v>
+        <v>51.76</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.512</v>
+        <v>0.533</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.513</v>
+        <v>0.535</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.919</v>
+        <v>0.966</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.104</v>
+        <v>0.097</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.024</v>
+        <v>0.044</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2556,19 +2556,19 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2580,13 +2580,13 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="U15" t="n">
         <v>6</v>
@@ -2595,28 +2595,28 @@
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -2631,54 +2631,54 @@
         <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.111</v>
+        <v>0.273</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>234:16</t>
+          <t>265:54</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>40.76</v>
+        <v>46.76</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.419</v>
+        <v>0.453</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.426</v>
+        <v>0.458</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.054</v>
+        <v>0.047</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.066</v>
+        <v>0.062</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="AY15" t="n">
         <v>0.005</v>
@@ -2691,156 +2691,156 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>31</v>
+      </c>
+      <c r="C16" t="n">
+        <v>483</v>
+      </c>
+      <c r="D16" t="n">
+        <v>119</v>
+      </c>
+      <c r="E16" t="n">
+        <v>201</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>145</v>
+      </c>
+      <c r="H16" t="n">
+        <v>104</v>
+      </c>
+      <c r="I16" t="n">
+        <v>131</v>
+      </c>
+      <c r="J16" t="n">
+        <v>84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" t="n">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
-        <v>429</v>
-      </c>
-      <c r="D16" t="n">
-        <v>109</v>
-      </c>
-      <c r="E16" t="n">
-        <v>181</v>
-      </c>
-      <c r="F16" t="n">
-        <v>40</v>
-      </c>
-      <c r="G16" t="n">
-        <v>129</v>
-      </c>
-      <c r="H16" t="n">
-        <v>91</v>
-      </c>
-      <c r="I16" t="n">
-        <v>117</v>
-      </c>
-      <c r="J16" t="n">
-        <v>76</v>
-      </c>
-      <c r="K16" t="n">
-        <v>64</v>
-      </c>
-      <c r="L16" t="n">
-        <v>27</v>
-      </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="T16" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
       <c r="U16" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="V16" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="W16" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="Z16" t="n">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.768</v>
+        <v>0.778</v>
       </c>
       <c r="AB16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.449</v>
+        <v>0.418</v>
       </c>
       <c r="AE16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF16" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.421</v>
+        <v>0.419</v>
       </c>
       <c r="AH16" t="n">
         <v>8</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.32</v>
+        <v>0.296</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AL16" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.308</v>
+        <v>0.331</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>738:58</t>
+          <t>821:57</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>401.48</v>
+        <v>447.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.545</v>
+        <v>0.548</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.593</v>
+        <v>0.598</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.069</v>
+        <v>1.079</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.9</v>
+        <v>1.909</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="17">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H17" t="n">
         <v>14</v>
@@ -2874,129 +2874,129 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M17" t="n">
         <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>14</v>
+      </c>
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="Q17" t="n">
-        <v>11</v>
-      </c>
-      <c r="R17" t="n">
-        <v>11</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
       <c r="T17" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.647</v>
+        <v>0.667</v>
       </c>
       <c r="AB17" t="n">
         <v>6</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.6</v>
+        <v>0.545</v>
       </c>
       <c r="AE17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.7</v>
+        <v>0.571</v>
       </c>
       <c r="AH17" t="n">
         <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.302</v>
+        <v>0.269</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>329:09</t>
+          <t>397:18</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>122.48</v>
+        <v>152.48</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.548</v>
+        <v>0.508</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.574</v>
+        <v>0.531</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.045</v>
+        <v>0.971</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.135</v>
+        <v>0.106</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.636</v>
+        <v>1.538</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.158</v>
+        <v>0.164</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.16</v>
+        <v>0.146</v>
       </c>
       <c r="AY17" t="n">
         <v>0.021</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3327,156 +3327,156 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C20" t="n">
+        <v>291</v>
+      </c>
+      <c r="D20" t="n">
+        <v>70</v>
+      </c>
+      <c r="E20" t="n">
+        <v>151</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>64</v>
+      </c>
+      <c r="I20" t="n">
+        <v>79</v>
+      </c>
+      <c r="J20" t="n">
+        <v>114</v>
+      </c>
+      <c r="K20" t="n">
+        <v>43</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>52</v>
+      </c>
+      <c r="R20" t="n">
+        <v>76</v>
+      </c>
+      <c r="S20" t="n">
+        <v>87</v>
+      </c>
+      <c r="T20" t="n">
+        <v>337</v>
+      </c>
+      <c r="U20" t="n">
         <v>25</v>
       </c>
-      <c r="C20" t="n">
-        <v>233</v>
-      </c>
-      <c r="D20" t="n">
-        <v>56</v>
-      </c>
-      <c r="E20" t="n">
-        <v>128</v>
-      </c>
-      <c r="F20" t="n">
-        <v>23</v>
-      </c>
-      <c r="G20" t="n">
-        <v>64</v>
-      </c>
-      <c r="H20" t="n">
-        <v>52</v>
-      </c>
-      <c r="I20" t="n">
-        <v>65</v>
-      </c>
-      <c r="J20" t="n">
-        <v>94</v>
-      </c>
-      <c r="K20" t="n">
-        <v>39</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19</v>
-      </c>
-      <c r="M20" t="n">
-        <v>31</v>
-      </c>
-      <c r="N20" t="n">
-        <v>9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>63</v>
-      </c>
-      <c r="S20" t="n">
-        <v>74</v>
-      </c>
-      <c r="T20" t="n">
-        <v>265</v>
-      </c>
-      <c r="U20" t="n">
-        <v>19</v>
-      </c>
       <c r="V20" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="W20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="Z20" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.385</v>
+        <v>0.455</v>
       </c>
       <c r="AH20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>0.333</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.364</v>
+        <v>0.397</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>480:18</t>
+          <t>571:31</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>265.6</v>
+        <v>312.76</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.471</v>
+        <v>0.502</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.528</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.877</v>
+        <v>0.93</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.169</v>
+        <v>0.166</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.271</v>
+        <v>0.283</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.089</v>
+        <v>2.192</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.095</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.115</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="21">
@@ -3626,13 +3626,13 @@
         <v>0.167</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.208</v>
+        <v>0.209</v>
       </c>
       <c r="AW21" t="n">
         <v>0.152</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="AY21" t="n">
         <v>0.002</v>
@@ -3645,156 +3645,156 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>32</v>
+      </c>
+      <c r="C22" t="n">
+        <v>333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>88</v>
+      </c>
+      <c r="E22" t="n">
+        <v>193</v>
+      </c>
+      <c r="F22" t="n">
         <v>28</v>
       </c>
-      <c r="C22" t="n">
-        <v>288</v>
-      </c>
-      <c r="D22" t="n">
-        <v>74</v>
-      </c>
-      <c r="E22" t="n">
-        <v>161</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
+        <v>120</v>
+      </c>
+      <c r="H22" t="n">
+        <v>73</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>62</v>
+      </c>
+      <c r="K22" t="n">
+        <v>114</v>
+      </c>
+      <c r="L22" t="n">
+        <v>51</v>
+      </c>
+      <c r="M22" t="n">
+        <v>32</v>
+      </c>
+      <c r="N22" t="n">
+        <v>23</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>44</v>
+      </c>
+      <c r="R22" t="n">
+        <v>79</v>
+      </c>
+      <c r="S22" t="n">
+        <v>102</v>
+      </c>
+      <c r="T22" t="n">
+        <v>370</v>
+      </c>
+      <c r="U22" t="n">
+        <v>67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>47</v>
+      </c>
+      <c r="W22" t="n">
         <v>24</v>
       </c>
-      <c r="G22" t="n">
-        <v>106</v>
-      </c>
-      <c r="H22" t="n">
-        <v>68</v>
-      </c>
-      <c r="I22" t="n">
-        <v>91</v>
-      </c>
-      <c r="J22" t="n">
-        <v>54</v>
-      </c>
-      <c r="K22" t="n">
-        <v>95</v>
-      </c>
-      <c r="L22" t="n">
-        <v>45</v>
-      </c>
-      <c r="M22" t="n">
-        <v>30</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="X22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>196</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AB22" t="n">
         <v>21</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>38</v>
-      </c>
-      <c r="R22" t="n">
-        <v>72</v>
-      </c>
-      <c r="S22" t="n">
-        <v>86</v>
-      </c>
-      <c r="T22" t="n">
-        <v>317</v>
-      </c>
-      <c r="U22" t="n">
-        <v>54</v>
-      </c>
-      <c r="V22" t="n">
-        <v>37</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>169</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>18</v>
-      </c>
       <c r="AC22" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.321</v>
+        <v>0.318</v>
       </c>
       <c r="AE22" t="n">
         <v>6</v>
       </c>
       <c r="AF22" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.222</v>
+        <v>0.194</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="AK22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.197</v>
+        <v>0.213</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>672:03</t>
+          <t>779:52</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>345.04</v>
+        <v>401</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.412</v>
+        <v>0.415</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.835</v>
+        <v>0.83</v>
       </c>
       <c r="AS22" t="n">
         <v>0.11</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.255</v>
+        <v>0.233</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.219</v>
+        <v>0.22</v>
       </c>
       <c r="AW22" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AY22" t="n">
         <v>0.06900000000000001</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0.068</v>
       </c>
     </row>
     <row r="23">
@@ -3804,100 +3804,100 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C23" t="n">
+        <v>304</v>
+      </c>
+      <c r="D23" t="n">
+        <v>121</v>
+      </c>
+      <c r="E23" t="n">
+        <v>213</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>59</v>
+      </c>
+      <c r="I23" t="n">
+        <v>87</v>
+      </c>
+      <c r="J23" t="n">
+        <v>46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>87</v>
+      </c>
+      <c r="L23" t="n">
+        <v>60</v>
+      </c>
+      <c r="M23" t="n">
+        <v>43</v>
+      </c>
+      <c r="N23" t="n">
+        <v>32</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>40</v>
+      </c>
+      <c r="R23" t="n">
+        <v>66</v>
+      </c>
+      <c r="S23" t="n">
+        <v>85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>429</v>
+      </c>
+      <c r="U23" t="n">
+        <v>43</v>
+      </c>
+      <c r="V23" t="n">
+        <v>65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>209</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AB23" t="n">
         <v>19</v>
       </c>
-      <c r="C23" t="n">
-        <v>250</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>180</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50</v>
-      </c>
-      <c r="I23" t="n">
-        <v>76</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>72</v>
-      </c>
-      <c r="L23" t="n">
-        <v>46</v>
-      </c>
-      <c r="M23" t="n">
-        <v>36</v>
-      </c>
-      <c r="N23" t="n">
-        <v>27</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>32</v>
-      </c>
-      <c r="R23" t="n">
-        <v>56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>73</v>
-      </c>
-      <c r="T23" t="n">
-        <v>346</v>
-      </c>
-      <c r="U23" t="n">
-        <v>41</v>
-      </c>
-      <c r="V23" t="n">
-        <v>51</v>
-      </c>
-      <c r="W23" t="n">
-        <v>9</v>
-      </c>
-      <c r="X23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>128</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>178</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>16</v>
-      </c>
       <c r="AC23" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="AE23" t="n">
         <v>6</v>
       </c>
       <c r="AF23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3909,51 +3909,51 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>462:26</t>
+          <t>567:45</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>247.44</v>
+        <v>294.28</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.549</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.58</v>
+        <v>0.598</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.033</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.129</v>
+        <v>0.136</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.188</v>
+        <v>1.15</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.228</v>
+        <v>0.222</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.103</v>
+        <v>0.11</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="24">
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AW24" t="n">
         <v>0.227</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4122,156 +4122,156 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="n">
+        <v>43</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>7</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>10</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="AI25" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="AJ25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>127:34</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU25" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>53:41</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>31</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.571</v>
-      </c>
       <c r="AV25" t="n">
-        <v>0.246</v>
+        <v>0.254</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.019</v>
+        <v>0.008</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.065</v>
+        <v>0.073</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -4281,16 +4281,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4299,25 +4299,25 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I26" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J26" t="n">
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L26" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M26" t="n">
         <v>7</v>
       </c>
       <c r="N26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4329,19 +4329,19 @@
         <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="S26" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T26" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="U26" t="n">
+        <v>36</v>
+      </c>
+      <c r="V26" t="n">
         <v>35</v>
-      </c>
-      <c r="V26" t="n">
-        <v>34</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
@@ -4350,31 +4350,31 @@
         <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="Z26" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.664</v>
+        <v>0.667</v>
       </c>
       <c r="AB26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC26" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.479</v>
+        <v>0.462</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -4396,26 +4396,26 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>424:33</t>
+          <t>453:21</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>195.08</v>
+        <v>207.48</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.553</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.584</v>
+        <v>0.588</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.994</v>
+        <v>1.012</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.149</v>
+        <v>0.14</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.27</v>
+        <v>0.295</v>
       </c>
       <c r="AU26" t="n">
         <v>0.655</v>
@@ -4424,13 +4424,13 @@
         <v>0.196</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="27">
@@ -4580,7 +4580,7 @@
         <v>1.525</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.242</v>
+        <v>0.243</v>
       </c>
       <c r="AW27" t="n">
         <v>0.024</v>
@@ -4589,7 +4589,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.076</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="28">
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="AW28" t="n">
         <v>0.07099999999999999</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4785,10 +4785,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L29" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4913,157 +4913,157 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2860</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="T30" t="n">
-        <v>57</v>
+        <v>3197</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1508</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>32</v>
+        <v>3005.88</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>0.951</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5072,148 +5072,148 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>2503</v>
+        <v>2961</v>
       </c>
       <c r="D31" t="n">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="E31" t="n">
-        <v>1263</v>
+        <v>1114</v>
       </c>
       <c r="F31" t="n">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="G31" t="n">
-        <v>686</v>
+        <v>946</v>
       </c>
       <c r="H31" t="n">
-        <v>501</v>
+        <v>648</v>
       </c>
       <c r="I31" t="n">
-        <v>689</v>
+        <v>844</v>
       </c>
       <c r="J31" t="n">
-        <v>501</v>
+        <v>610</v>
       </c>
       <c r="K31" t="n">
-        <v>658</v>
+        <v>846</v>
       </c>
       <c r="L31" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M31" t="n">
-        <v>290</v>
+        <v>227</v>
       </c>
       <c r="N31" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>390</v>
+        <v>514</v>
       </c>
       <c r="Q31" t="n">
-        <v>358</v>
+        <v>495</v>
       </c>
       <c r="R31" t="n">
-        <v>687</v>
+        <v>738</v>
       </c>
       <c r="S31" t="n">
-        <v>647</v>
+        <v>766</v>
       </c>
       <c r="T31" t="n">
-        <v>2788</v>
+        <v>3428</v>
       </c>
       <c r="U31" t="n">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="V31" t="n">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="W31" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="X31" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="Y31" t="n">
-        <v>960</v>
+        <v>1072</v>
       </c>
       <c r="Z31" t="n">
-        <v>1333</v>
+        <v>1408</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.72</v>
+        <v>0.761</v>
       </c>
       <c r="AB31" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AC31" t="n">
-        <v>386</v>
+        <v>316</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.399</v>
+        <v>0.449</v>
       </c>
       <c r="AE31" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="AF31" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3</v>
+        <v>0.389</v>
       </c>
       <c r="AH31" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="AI31" t="n">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.288</v>
+        <v>0.459</v>
       </c>
       <c r="AK31" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="AL31" t="n">
-        <v>523</v>
+        <v>724</v>
       </c>
       <c r="AM31" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>6425:00</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>2945.36</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.315</v>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>5625:00</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>2642.16</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.257</v>
-      </c>
       <c r="AU31" t="n">
-        <v>1.285</v>
+        <v>1.187</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
@@ -5222,7 +5222,7 @@
         <v>0.064</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5231,476 +5231,476 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" t="n">
-        <v>2606</v>
-      </c>
-      <c r="D32" t="n">
-        <v>568</v>
-      </c>
-      <c r="E32" t="n">
-        <v>975</v>
-      </c>
-      <c r="F32" t="n">
-        <v>294</v>
-      </c>
-      <c r="G32" t="n">
-        <v>819</v>
-      </c>
-      <c r="H32" t="n">
-        <v>588</v>
-      </c>
-      <c r="I32" t="n">
-        <v>768</v>
-      </c>
-      <c r="J32" t="n">
-        <v>540</v>
-      </c>
-      <c r="K32" t="n">
-        <v>737</v>
-      </c>
-      <c r="L32" t="n">
-        <v>304</v>
-      </c>
-      <c r="M32" t="n">
-        <v>200</v>
-      </c>
-      <c r="N32" t="n">
-        <v>159</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>454</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>437</v>
-      </c>
-      <c r="R32" t="n">
-        <v>648</v>
-      </c>
-      <c r="S32" t="n">
-        <v>684</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3016</v>
-      </c>
-      <c r="U32" t="n">
-        <v>316</v>
-      </c>
-      <c r="V32" t="n">
-        <v>305</v>
-      </c>
-      <c r="W32" t="n">
-        <v>188</v>
-      </c>
-      <c r="X32" t="n">
-        <v>121</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>956</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1261</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>124</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>278</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>76</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>204</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>95</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>197</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>199</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>622</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>5625:00</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>2585.92</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.189</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
+          <t>#00 J. SAMUELS (Per Game)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10.062</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.281</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="T33" t="n">
+        <v>349</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4.188</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.656</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>9.669</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.041</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#00 J. SAMUELS (Per Game)</t>
+          <t>#2 M. BELLA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>10.393</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3.464</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>5.036</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.857</v>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.643</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.714</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.679</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.393</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.286</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>311</v>
+        <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>2.357</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.321</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.893</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.487</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AK34" t="n">
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
         <v>0.5</v>
       </c>
-      <c r="AL34" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>21:03</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>9.766</v>
-      </c>
       <c r="AP34" t="n">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.064</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.681</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.198</v>
+        <v>0.282</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.149</v>
+        <v>0.767</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#2 M. BELLA (Per Game)</t>
+          <t>#3 Y. NZOSA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2.323</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.968</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.645</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.065</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>0.742</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="R35" t="n">
-        <v>0.5</v>
+        <v>1.452</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="T35" t="n">
-        <v>-1</v>
+        <v>61</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.677</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5718,148 +5718,148 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.5</v>
+        <v>0.065</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0.5</v>
+        <v>2.205</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.281</v>
+        <v>0.151</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.771</v>
+        <v>0.138</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#3 Y. NZOSA (Per Game)</t>
+          <t>#5 R. RODRÍGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>2.481</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.037</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.481</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.481</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.519</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.148</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.481</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -5877,91 +5877,91 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.277</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#5 R. RODRÍGUEZ (Per Game)</t>
+          <t>#5 J. SHACKELFORD (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>4.167</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5970,1966 +5970,1966 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>6.213</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.671</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#5 J. SHACKELFORD (Per Game)</t>
+          <t>#6 J. GUDMUNDSSON (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>4.821</v>
       </c>
       <c r="D38" t="n">
-        <v>0.75</v>
+        <v>0.786</v>
       </c>
       <c r="E38" t="n">
-        <v>2.75</v>
+        <v>2.107</v>
       </c>
       <c r="F38" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="T38" t="n">
+        <v>167</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.464</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0.25</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="AC38" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0.25</v>
       </c>
-      <c r="M38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>14</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AG38" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI38" t="n">
         <v>0.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>1</v>
+        <v>1.857</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.25</v>
+        <v>0.269</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>5.6</v>
+        <v>6.576</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.265</v>
+        <v>0.392</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.374</v>
+        <v>0.462</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.714</v>
+        <v>0.733</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.045</v>
+        <v>0.206</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.412</v>
+        <v>0.296</v>
       </c>
       <c r="AU38" t="n">
-        <v>3</v>
+        <v>2.395</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.197</v>
+        <v>0.135</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.121</v>
+        <v>0.098</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.024</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#6 J. GUDMUNDSSON (Per Game)</t>
+          <t>#7 J. RUBIO (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>5.542</v>
+        <v>1.667</v>
       </c>
       <c r="D39" t="n">
-        <v>0.917</v>
+        <v>0.3</v>
       </c>
       <c r="E39" t="n">
-        <v>2.375</v>
+        <v>0.433</v>
       </c>
       <c r="F39" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>2.542</v>
+        <v>1.067</v>
       </c>
       <c r="H39" t="n">
-        <v>1.458</v>
+        <v>0.067</v>
       </c>
       <c r="I39" t="n">
-        <v>1.917</v>
+        <v>0.133</v>
       </c>
       <c r="J39" t="n">
-        <v>3.542</v>
+        <v>0.067</v>
       </c>
       <c r="K39" t="n">
-        <v>1.708</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="T39" t="n">
+        <v>40</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.333</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.458</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.458</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="T39" t="n">
-        <v>161</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD39" t="n">
         <v>0.333</v>
       </c>
-      <c r="Y39" t="n">
-        <v>2.083</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.233</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.292</v>
+        <v>0.033</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.167</v>
+        <v>0.067</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.583</v>
+        <v>0.333</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.286</v>
+        <v>0.2</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.583</v>
+        <v>0.267</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.958</v>
+        <v>0.733</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.298</v>
+        <v>0.364</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>7.218</v>
+        <v>1.725</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.415</v>
+        <v>0.533</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.481</v>
+        <v>0.535</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.768</v>
+        <v>0.966</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.202</v>
+        <v>0.097</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.297</v>
+        <v>0.044</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.429</v>
+        <v>0.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.016</v>
+        <v>0.094</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.117</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#7 J. RUBIO (Per Game)</t>
+          <t>#8 P. ALMAZÁN (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>1.692</v>
+        <v>1.367</v>
       </c>
       <c r="D40" t="n">
-        <v>0.308</v>
+        <v>0.3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.462</v>
+        <v>0.533</v>
       </c>
       <c r="F40" t="n">
-        <v>0.346</v>
+        <v>0.233</v>
       </c>
       <c r="G40" t="n">
-        <v>1.154</v>
+        <v>0.9</v>
       </c>
       <c r="H40" t="n">
-        <v>0.038</v>
+        <v>0.067</v>
       </c>
       <c r="I40" t="n">
-        <v>0.077</v>
+        <v>0.133</v>
       </c>
       <c r="J40" t="n">
-        <v>0.038</v>
+        <v>0.167</v>
       </c>
       <c r="K40" t="n">
-        <v>0.615</v>
+        <v>0.367</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="M40" t="n">
-        <v>0.308</v>
+        <v>0.633</v>
       </c>
       <c r="N40" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.192</v>
+        <v>0.067</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.192</v>
+        <v>0.067</v>
       </c>
       <c r="R40" t="n">
-        <v>1.192</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>0.115</v>
+        <v>0.2</v>
       </c>
       <c r="T40" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U40" t="n">
-        <v>0.346</v>
+        <v>0.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0.385</v>
+        <v>0.067</v>
       </c>
       <c r="W40" t="n">
-        <v>0.115</v>
+        <v>0.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0.038</v>
+        <v>0.067</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.308</v>
+        <v>0.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.385</v>
+        <v>0.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.038</v>
+        <v>0.067</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.115</v>
+        <v>0.133</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.038</v>
+        <v>0.233</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.077</v>
+        <v>0.133</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.385</v>
+        <v>0.533</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.269</v>
+        <v>0.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.769</v>
+        <v>0.367</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.35</v>
+        <v>0.273</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>1.842</v>
+        <v>1.559</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.512</v>
+        <v>0.453</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.513</v>
+        <v>0.458</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.919</v>
+        <v>0.877</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.104</v>
+        <v>0.043</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.024</v>
+        <v>0.047</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.101</v>
+        <v>0.075</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.092</v>
+        <v>0.062</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.092</v>
+        <v>0.048</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#8 P. ALMAZÁN (Per Game)</t>
+          <t>#10 G. CORBALÁN (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C41" t="n">
-        <v>1.269</v>
+        <v>15.581</v>
       </c>
       <c r="D41" t="n">
-        <v>0.308</v>
+        <v>3.839</v>
       </c>
       <c r="E41" t="n">
-        <v>0.538</v>
+        <v>6.484</v>
       </c>
       <c r="F41" t="n">
-        <v>0.192</v>
+        <v>1.516</v>
       </c>
       <c r="G41" t="n">
-        <v>0.885</v>
+        <v>4.677</v>
       </c>
       <c r="H41" t="n">
-        <v>0.077</v>
+        <v>3.355</v>
       </c>
       <c r="I41" t="n">
-        <v>0.154</v>
+        <v>4.226</v>
       </c>
       <c r="J41" t="n">
-        <v>0.154</v>
+        <v>2.71</v>
       </c>
       <c r="K41" t="n">
-        <v>0.385</v>
+        <v>2.226</v>
       </c>
       <c r="L41" t="n">
-        <v>0.577</v>
+        <v>0.903</v>
       </c>
       <c r="M41" t="n">
-        <v>0.654</v>
+        <v>1.516</v>
       </c>
       <c r="N41" t="n">
-        <v>0.038</v>
+        <v>0.613</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.077</v>
+        <v>1.419</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.077</v>
+        <v>1.419</v>
       </c>
       <c r="R41" t="n">
-        <v>1.231</v>
+        <v>1.516</v>
       </c>
       <c r="S41" t="n">
-        <v>0.192</v>
+        <v>3.71</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>547</v>
       </c>
       <c r="U41" t="n">
-        <v>0.231</v>
+        <v>2.29</v>
       </c>
       <c r="V41" t="n">
-        <v>0.077</v>
+        <v>1.419</v>
       </c>
       <c r="W41" t="n">
-        <v>0.038</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0.038</v>
+        <v>0.613</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.192</v>
+        <v>5.871</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.308</v>
+        <v>7.548</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.625</v>
+        <v>0.778</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.077</v>
+        <v>0.742</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.115</v>
+        <v>1.774</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.667</v>
+        <v>0.418</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.115</v>
+        <v>0.581</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.269</v>
+        <v>1.387</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.154</v>
+        <v>0.258</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.538</v>
+        <v>0.871</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.286</v>
+        <v>0.296</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.038</v>
+        <v>1.258</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.346</v>
+        <v>3.806</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.111</v>
+        <v>0.331</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>26:30</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>1.568</v>
+        <v>14.44</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.419</v>
+        <v>0.548</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.426</v>
+        <v>0.598</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.079</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.049</v>
+        <v>0.098</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.054</v>
+        <v>0.301</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>1.909</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.074</v>
+        <v>0.233</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.066</v>
+        <v>0.035</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.05</v>
+        <v>0.098</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.005</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#10 G. CORBALÁN (Per Game)</t>
+          <t>#11 D. DÍEZ (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C42" t="n">
-        <v>15.321</v>
+        <v>7.048</v>
       </c>
       <c r="D42" t="n">
-        <v>3.893</v>
+        <v>1.333</v>
       </c>
       <c r="E42" t="n">
-        <v>6.464</v>
+        <v>2.381</v>
       </c>
       <c r="F42" t="n">
-        <v>1.429</v>
+        <v>1.238</v>
       </c>
       <c r="G42" t="n">
-        <v>4.607</v>
+        <v>3.905</v>
       </c>
       <c r="H42" t="n">
-        <v>3.25</v>
+        <v>0.667</v>
       </c>
       <c r="I42" t="n">
-        <v>4.179</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>2.714</v>
+        <v>0.952</v>
       </c>
       <c r="K42" t="n">
-        <v>2.286</v>
+        <v>2.381</v>
       </c>
       <c r="L42" t="n">
-        <v>0.964</v>
+        <v>0.952</v>
       </c>
       <c r="M42" t="n">
-        <v>1.5</v>
+        <v>0.286</v>
       </c>
       <c r="N42" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="T42" t="n">
+        <v>152</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.571</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.714</v>
-      </c>
-      <c r="T42" t="n">
-        <v>489</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>5.786</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>7.536</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.421</v>
-      </c>
       <c r="AH42" t="n">
-        <v>0.286</v>
+        <v>0.381</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.893</v>
+        <v>0.714</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.32</v>
+        <v>0.533</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.143</v>
+        <v>0.857</v>
       </c>
       <c r="AL42" t="n">
-        <v>3.714</v>
+        <v>3.19</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.308</v>
+        <v>0.269</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>26:23</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>14.339</v>
+        <v>7.261</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.545</v>
+        <v>0.508</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.593</v>
+        <v>0.531</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.069</v>
+        <v>0.971</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.1</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.294</v>
+        <v>0.106</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.9</v>
+        <v>1.538</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.231</v>
+        <v>0.164</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.101</v>
+        <v>0.146</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.102</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#11 D. DÍEZ (Per Game)</t>
+          <t>#12 A. REYES (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>7.529</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.235</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2.176</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.412</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.941</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
-        <v>1.059</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.647</v>
-      </c>
       <c r="L43" t="n">
-        <v>1.118</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.294</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.471</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>3.118</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>7.205</v>
+        <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.045</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.636</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.16</v>
+        <v>0.392</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#12 A. REYES (Per Game)</t>
+          <t>#17 S. GARCÍA (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>02:58</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.394</v>
+        <v>0.093</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#17 S. GARCÍA (Per Game)</t>
+          <t>#19 R. NETO (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6</v>
+        <v>10.034</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2.414</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2</v>
+        <v>5.207</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4</v>
+        <v>2.586</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.724</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6</v>
+        <v>3.931</v>
       </c>
       <c r="K45" t="n">
-        <v>0.4</v>
+        <v>1.483</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4</v>
+        <v>1.414</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8</v>
+        <v>1.793</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.8</v>
+        <v>1.793</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8</v>
+        <v>2.621</v>
       </c>
       <c r="S45" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>337</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.862</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.276</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>3.586</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>5.069</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.2</v>
+        <v>1.724</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.138</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.2</v>
+        <v>0.414</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.2</v>
+        <v>0.862</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.2</v>
+        <v>2.172</v>
       </c>
       <c r="AM45" t="n">
-        <v>1</v>
+        <v>0.397</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>05:01</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>1.4</v>
+        <v>10.785</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.5</v>
+        <v>0.502</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.429</v>
+        <v>0.93</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.571</v>
+        <v>0.166</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.75</v>
+        <v>2.192</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.119</v>
+        <v>0.234</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.083</v>
+        <v>0.036</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.019</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#19 R. NETO (Per Game)</t>
+          <t>#22 S. DE SOUSA (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>9.32</v>
+        <v>6.2</v>
       </c>
       <c r="D46" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="E46" t="n">
-        <v>5.12</v>
+        <v>3.3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
-        <v>3.76</v>
+        <v>0.2</v>
       </c>
       <c r="K46" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.76</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>1.24</v>
+        <v>0.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0.36</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="T46" t="n">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="U46" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="V46" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="W46" t="n">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
       <c r="X46" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.92</v>
+        <v>6.1</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.639</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.76</v>
+        <v>0.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.295</v>
+        <v>0.333</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>10.624</v>
+        <v>5.996</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.471</v>
+        <v>0.636</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.528</v>
+        <v>0.646</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.877</v>
+        <v>1.034</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.169</v>
+        <v>0.2</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.271</v>
+        <v>0.606</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.089</v>
+        <v>0.167</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.235</v>
+        <v>0.209</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.041</v>
+        <v>0.152</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.095</v>
+        <v>0.237</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.131</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#22 S. DE SOUSA (Per Game)</t>
+          <t>#23 L. MEINDL (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>6.2</v>
+        <v>10.406</v>
       </c>
       <c r="D47" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="E47" t="n">
-        <v>3.3</v>
+        <v>6.031</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>2.281</v>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>3.125</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2</v>
+        <v>1.938</v>
       </c>
       <c r="K47" t="n">
-        <v>2.5</v>
+        <v>3.562</v>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>1.594</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0.719</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.2</v>
+        <v>1.375</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.2</v>
+        <v>1.375</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>2.469</v>
       </c>
       <c r="S47" t="n">
-        <v>2.5</v>
+        <v>3.188</v>
       </c>
       <c r="T47" t="n">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="U47" t="n">
-        <v>0.4</v>
+        <v>2.094</v>
       </c>
       <c r="V47" t="n">
-        <v>1.9</v>
+        <v>1.469</v>
       </c>
       <c r="W47" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.9</v>
+        <v>4.188</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.1</v>
+        <v>6.125</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.639</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.2</v>
+        <v>0.656</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.6</v>
+        <v>2.062</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.344</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.213</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>24:22</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.996</v>
+        <v>12.531</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.636</v>
+        <v>0.415</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.646</v>
+        <v>0.466</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.034</v>
+        <v>0.83</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.606</v>
+        <v>0.233</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.167</v>
+        <v>1.409</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.208</v>
+        <v>0.22</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.152</v>
+        <v>0.068</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.238</v>
+        <v>0.17</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.007</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#23 L. MEINDL (Per Game)</t>
+          <t>#27 E. HAPP (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C48" t="n">
-        <v>10.286</v>
+        <v>13.217</v>
       </c>
       <c r="D48" t="n">
-        <v>2.643</v>
+        <v>5.261</v>
       </c>
       <c r="E48" t="n">
-        <v>5.75</v>
+        <v>9.260999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.857</v>
+        <v>0.043</v>
       </c>
       <c r="G48" t="n">
-        <v>3.786</v>
+        <v>0.13</v>
       </c>
       <c r="H48" t="n">
-        <v>2.429</v>
+        <v>2.565</v>
       </c>
       <c r="I48" t="n">
-        <v>3.25</v>
+        <v>3.783</v>
       </c>
       <c r="J48" t="n">
-        <v>1.929</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>3.393</v>
+        <v>3.783</v>
       </c>
       <c r="L48" t="n">
-        <v>1.607</v>
+        <v>2.609</v>
       </c>
       <c r="M48" t="n">
-        <v>1.071</v>
+        <v>1.87</v>
       </c>
       <c r="N48" t="n">
-        <v>0.75</v>
+        <v>1.391</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.357</v>
+        <v>1.739</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.357</v>
+        <v>1.739</v>
       </c>
       <c r="R48" t="n">
-        <v>2.571</v>
+        <v>2.87</v>
       </c>
       <c r="S48" t="n">
-        <v>3.071</v>
+        <v>3.696</v>
       </c>
       <c r="T48" t="n">
-        <v>317</v>
+        <v>429</v>
       </c>
       <c r="U48" t="n">
-        <v>1.929</v>
+        <v>1.87</v>
       </c>
       <c r="V48" t="n">
-        <v>1.321</v>
+        <v>2.826</v>
       </c>
       <c r="W48" t="n">
-        <v>0.821</v>
+        <v>0.478</v>
       </c>
       <c r="X48" t="n">
-        <v>0.536</v>
+        <v>0.304</v>
       </c>
       <c r="Y48" t="n">
-        <v>4.214</v>
+        <v>6.739</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.036</v>
+        <v>9.087</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.698</v>
+        <v>0.742</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.643</v>
+        <v>0.826</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>2.522</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.321</v>
+        <v>0.328</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.214</v>
+        <v>0.261</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.964</v>
+        <v>1.435</v>
       </c>
       <c r="AG48" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>24:41</t>
+        </is>
+      </c>
+      <c r="AO48" t="n">
+        <v>12.795</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AV48" t="n">
         <v>0.222</v>
       </c>
-      <c r="AH48" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>12.323</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="AS48" t="n">
+      <c r="AW48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AT48" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>1.421</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.06900000000000001</v>
-      </c>
       <c r="AX48" t="n">
-        <v>0.165</v>
+        <v>0.178</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.068</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#27 E. HAPP (Per Game)</t>
+          <t>#32 A. LIMA (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>13.158</v>
+        <v>0.5</v>
       </c>
       <c r="D49" t="n">
-        <v>5.263</v>
+        <v>0.167</v>
       </c>
       <c r="E49" t="n">
-        <v>9.474</v>
+        <v>0.333</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.632</v>
+        <v>0.167</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>0.333</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.789</v>
+        <v>0.333</v>
       </c>
       <c r="L49" t="n">
-        <v>2.421</v>
+        <v>0.667</v>
       </c>
       <c r="M49" t="n">
-        <v>1.895</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.421</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.684</v>
+        <v>0.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.684</v>
+        <v>0.5</v>
       </c>
       <c r="R49" t="n">
-        <v>2.947</v>
+        <v>1.333</v>
       </c>
       <c r="S49" t="n">
-        <v>3.842</v>
+        <v>0.167</v>
       </c>
       <c r="T49" t="n">
-        <v>346</v>
+        <v>-3</v>
       </c>
       <c r="U49" t="n">
-        <v>2.158</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>2.684</v>
+        <v>0.5</v>
       </c>
       <c r="W49" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.737</v>
+        <v>0.167</v>
       </c>
       <c r="Z49" t="n">
-        <v>9.368</v>
+        <v>0.333</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.719</v>
+        <v>0.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.842</v>
+        <v>0.167</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.526</v>
+        <v>0.333</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.579</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
         <v>0</v>
@@ -7944,775 +7944,775 @@
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>24:20</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>13.023</v>
+        <v>0.98</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.549</v>
+        <v>0.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.58</v>
+        <v>0.521</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.129</v>
+        <v>0.51</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.275</v>
+        <v>0.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.188</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.228</v>
+        <v>0.138</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.103</v>
+        <v>0.227</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.182</v>
+        <v>0.127</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#32 A. LIMA (Per Game)</t>
+          <t>#33 M. HEIDEGGER (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5</v>
+        <v>10.429</v>
       </c>
       <c r="D50" t="n">
-        <v>0.167</v>
+        <v>1.429</v>
       </c>
       <c r="E50" t="n">
-        <v>0.333</v>
+        <v>2.429</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>5.429</v>
       </c>
       <c r="H50" t="n">
-        <v>0.167</v>
+        <v>1.571</v>
       </c>
       <c r="I50" t="n">
-        <v>0.333</v>
+        <v>1.857</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="K50" t="n">
-        <v>0.333</v>
+        <v>1.143</v>
       </c>
       <c r="L50" t="n">
-        <v>0.667</v>
+        <v>0.143</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>2.143</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5</v>
+        <v>2.143</v>
       </c>
       <c r="R50" t="n">
-        <v>1.333</v>
+        <v>2.571</v>
       </c>
       <c r="S50" t="n">
-        <v>0.167</v>
+        <v>1.571</v>
       </c>
       <c r="T50" t="n">
-        <v>-3</v>
+        <v>43</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="V50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.167</v>
+        <v>2.286</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.333</v>
+        <v>3</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.5</v>
+        <v>0.762</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.167</v>
+        <v>0.429</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.333</v>
+        <v>0.571</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>4.857</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>03:02</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>0.98</v>
+        <v>10.817</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.5</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.521</v>
+        <v>0.601</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.51</v>
+        <v>0.964</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.51</v>
+        <v>0.198</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.137</v>
+        <v>0.254</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.227</v>
+        <v>0.008</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.128</v>
+        <v>0.073</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#33 M. HEIDEGGER (Per Game)</t>
+          <t>#40 L. FISCHER (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>2.964</v>
       </c>
       <c r="E51" t="n">
-        <v>3.333</v>
+        <v>5.321</v>
       </c>
       <c r="F51" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>4.667</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>2.393</v>
       </c>
       <c r="J51" t="n">
-        <v>1.333</v>
+        <v>0.679</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>1.821</v>
       </c>
       <c r="L51" t="n">
-        <v>0.333</v>
+        <v>1.179</v>
       </c>
       <c r="M51" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0.333</v>
+        <v>1.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.333</v>
+        <v>1.036</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.333</v>
+        <v>1.036</v>
       </c>
       <c r="R51" t="n">
-        <v>3.333</v>
+        <v>2.464</v>
       </c>
       <c r="S51" t="n">
-        <v>0.333</v>
+        <v>1.893</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="Y51" t="n">
-        <v>1</v>
+        <v>3.571</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.667</v>
+        <v>5.357</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.667</v>
+        <v>0.857</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.667</v>
+        <v>1.857</v>
       </c>
       <c r="AD51" t="n">
-        <v>1</v>
+        <v>0.462</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.333</v>
+        <v>0.107</v>
       </c>
       <c r="AF51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.333</v>
+        <v>0.214</v>
       </c>
       <c r="AH51" t="n">
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>4.333</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>10.333</v>
+        <v>7.41</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.5</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.5</v>
+        <v>0.588</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.774</v>
+        <v>1.012</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.226</v>
+        <v>0.14</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.571</v>
+        <v>0.655</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.246</v>
+        <v>0.196</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.019</v>
+        <v>0.075</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.065</v>
+        <v>0.131</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.047</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#40 L. FISCHER (Per Game)</t>
+          <t>#56 J. JACKSON (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C52" t="n">
-        <v>7.462</v>
+        <v>14.6</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="E52" t="n">
-        <v>5.423</v>
+        <v>5.05</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>1.462</v>
+        <v>3.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2.192</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
-        <v>0.731</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>1.923</v>
+        <v>1.9</v>
       </c>
       <c r="L52" t="n">
-        <v>1.192</v>
+        <v>0.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0.269</v>
+        <v>1.65</v>
       </c>
       <c r="N52" t="n">
-        <v>1.308</v>
+        <v>0.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.115</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.115</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="S52" t="n">
-        <v>1.808</v>
+        <v>3.75</v>
       </c>
       <c r="T52" t="n">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="U52" t="n">
-        <v>1.346</v>
+        <v>2.45</v>
       </c>
       <c r="V52" t="n">
-        <v>1.308</v>
+        <v>1.15</v>
       </c>
       <c r="W52" t="n">
-        <v>0.308</v>
+        <v>1.1</v>
       </c>
       <c r="X52" t="n">
-        <v>0.154</v>
+        <v>0.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.269</v>
+        <v>4.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.664</v>
+        <v>0.847</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.885</v>
+        <v>0.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.846</v>
+        <v>1.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.479</v>
+        <v>0.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.077</v>
+        <v>0.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.154</v>
+        <v>0.306</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>25:50</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>7.503</v>
+        <v>14.678</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.553</v>
+        <v>0.516</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.584</v>
+        <v>0.576</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.994</v>
+        <v>0.995</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.149</v>
+        <v>0.136</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.655</v>
+        <v>1.525</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.196</v>
+        <v>0.243</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.076</v>
+        <v>0.024</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.138</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.025</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>#56 J. JACKSON (Per Game)</t>
+          <t>#59 J. TABOADA (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>14.6</v>
+        <v>3.25</v>
       </c>
       <c r="D53" t="n">
-        <v>2.4</v>
+        <v>0.75</v>
       </c>
       <c r="E53" t="n">
-        <v>5.05</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="H53" t="n">
-        <v>3.2</v>
+        <v>0.25</v>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>0.25</v>
       </c>
       <c r="J53" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="K53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="M53" t="n">
-        <v>1.65</v>
+        <v>0.25</v>
       </c>
       <c r="N53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>0.2</v>
       </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T53" t="n">
-        <v>274</v>
-      </c>
-      <c r="U53" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD53" t="n">
+      <c r="AK53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL53" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE53" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AM53" t="n">
-        <v>0.387</v>
+        <v>0.5</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>25:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>14.678</v>
+        <v>3.86</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.516</v>
+        <v>0.4</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.576</v>
+        <v>0.421</v>
       </c>
       <c r="AR53" t="n">
-        <v>0.995</v>
+        <v>0.842</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.29</v>
+        <v>0.067</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.525</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.242</v>
+        <v>0.152</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.024</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>0.111</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>#59 J. TABOADA (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>2.094</v>
       </c>
       <c r="L54" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.25</v>
+        <v>0.188</v>
       </c>
       <c r="S54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -8721,222 +8721,222 @@
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.842</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
         <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
         <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
         <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>89.375</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>24.094</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>44.75</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>7.781</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>24.781</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>17.844</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>24.281</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>17.719</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>23.438</v>
       </c>
       <c r="L55" t="n">
-        <v>1.357</v>
+        <v>12.312</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.143</v>
+        <v>13.719</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>12.656</v>
       </c>
       <c r="R55" t="n">
-        <v>0.179</v>
+        <v>24.031</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3197</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>13.781</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>11.688</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>3.625</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>34.156</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>47.125</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>13.719</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.594</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>6.188</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>19.125</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>93.934</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>0.951</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AY55" t="n">
         <v>0</v>
@@ -8945,477 +8945,159 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>92.53100000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>20.531</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>34.812</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>10.406</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>29.562</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>26.375</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>19.062</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>26.438</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>11.094</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>7.094</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>16.062</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>15.469</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>23.062</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>23.938</v>
       </c>
       <c r="T56" t="n">
-        <v>57</v>
+        <v>3428</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>11.031</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>11.156</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>6.531</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4.188</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>4.438</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>9.875</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.844</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>7.312</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>3.188</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>6.938</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>7.219</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>22.625</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>0.319</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>1.143</v>
+        <v>92.04300000000001</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.005</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>28</v>
-      </c>
-      <c r="C57" t="n">
-        <v>89.393</v>
-      </c>
-      <c r="D57" t="n">
-        <v>24.393</v>
-      </c>
-      <c r="E57" t="n">
-        <v>45.107</v>
-      </c>
-      <c r="F57" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="G57" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>17.893</v>
-      </c>
-      <c r="I57" t="n">
-        <v>24.607</v>
-      </c>
-      <c r="J57" t="n">
-        <v>17.893</v>
-      </c>
-      <c r="K57" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>12.429</v>
-      </c>
-      <c r="M57" t="n">
-        <v>10.357</v>
-      </c>
-      <c r="N57" t="n">
-        <v>5.714</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>13.929</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>12.786</v>
-      </c>
-      <c r="R57" t="n">
-        <v>24.536</v>
-      </c>
-      <c r="S57" t="n">
-        <v>23.107</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2788</v>
-      </c>
-      <c r="U57" t="n">
-        <v>14</v>
-      </c>
-      <c r="V57" t="n">
-        <v>11.536</v>
-      </c>
-      <c r="W57" t="n">
-        <v>6.071</v>
-      </c>
-      <c r="X57" t="n">
-        <v>3.607</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>34.286</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>47.607</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>13.786</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>8.321</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.679</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>5.821</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>5.893</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>18.679</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO57" t="n">
-        <v>94.363</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>28</v>
-      </c>
-      <c r="C58" t="n">
-        <v>93.071</v>
-      </c>
-      <c r="D58" t="n">
-        <v>20.286</v>
-      </c>
-      <c r="E58" t="n">
-        <v>34.821</v>
-      </c>
-      <c r="F58" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="H58" t="n">
-        <v>21</v>
-      </c>
-      <c r="I58" t="n">
-        <v>27.429</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19.286</v>
-      </c>
-      <c r="K58" t="n">
-        <v>26.321</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10.857</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="N58" t="n">
-        <v>5.679</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>16.214</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>15.607</v>
-      </c>
-      <c r="R58" t="n">
-        <v>23.143</v>
-      </c>
-      <c r="S58" t="n">
-        <v>24.429</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3016</v>
-      </c>
-      <c r="U58" t="n">
-        <v>11.286</v>
-      </c>
-      <c r="V58" t="n">
-        <v>10.893</v>
-      </c>
-      <c r="W58" t="n">
-        <v>6.714</v>
-      </c>
-      <c r="X58" t="n">
-        <v>4.321</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>34.143</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>45.036</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>4.429</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>9.929</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>2.714</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>7.286</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>3.393</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>7.036</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>7.107</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>22.214</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO58" t="n">
-        <v>92.354</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>1.189</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AY58" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Recoletas Salud San Pablo Burgos.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Recoletas Salud San Pablo Burgos.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2611.88</v>
+        <v>2771.52</v>
       </c>
       <c r="C2" t="n">
-        <v>2601.12</v>
+        <v>2761</v>
       </c>
       <c r="D2" t="n">
-        <v>109.9526357876607</v>
+        <v>110.4310032596885</v>
       </c>
       <c r="E2" t="n">
-        <v>113.8355785200222</v>
+        <v>114.1615356754799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5143820224719101</v>
+        <v>0.5181434599156118</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1460470810544666</v>
+        <v>0.1468139188360067</v>
       </c>
       <c r="H2" t="n">
-        <v>0.317741935483871</v>
+        <v>0.3221629855293222</v>
       </c>
       <c r="I2" t="n">
-        <v>0.256629213483146</v>
+        <v>0.250210970464135</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="N2" t="n">
-        <v>1093</v>
+        <v>1151</v>
       </c>
       <c r="O2" t="n">
-        <v>1508</v>
+        <v>1591</v>
       </c>
       <c r="P2" t="n">
-        <v>0.677752808988764</v>
+        <v>0.6713080168776371</v>
       </c>
       <c r="Q2" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="R2" t="n">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1973033707865169</v>
+        <v>0.1953586497890295</v>
       </c>
       <c r="T2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U2" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="V2" t="n">
-        <v>0.117752808988764</v>
+        <v>0.1160337552742616</v>
       </c>
       <c r="W2" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="X2" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08134831460674158</v>
+        <v>0.0839662447257384</v>
       </c>
       <c r="Z2" t="n">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="AA2" t="n">
-        <v>612</v>
+        <v>650</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2750561797752809</v>
+        <v>0.2742616033755274</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7248010610079576</v>
+        <v>0.7234443746071653</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3826879271070615</v>
+        <v>0.3779697624190065</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3091603053435115</v>
+        <v>0.3054545454545455</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.281767955801105</v>
+        <v>0.2914572864321608</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3323076923076923</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.449602122015915</v>
+        <v>1.446888749214331</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6183206106870229</v>
+        <v>0.610909090909091</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9419924337957125</v>
+        <v>0.9681978798586572</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.857976653696498</v>
+        <v>0.8621323529411765</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.949238578680203</v>
+        <v>0.9716312056737588</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.655172413793103</v>
+        <v>1.669491525423729</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.291571753986333</v>
+        <v>1.29637526652452</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.068337129840547</v>
+        <v>5.053304904051172</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.359908883826879</v>
+        <v>6.349680170575693</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.62124999999999</v>
+        <v>81.51529411764706</v>
       </c>
       <c r="C3" t="n">
-        <v>81.285</v>
+        <v>81.20588235294116</v>
       </c>
       <c r="D3" t="n">
-        <v>109.9526357876607</v>
+        <v>110.4310032596886</v>
       </c>
       <c r="E3" t="n">
-        <v>113.8355785200222</v>
+        <v>114.1615356754799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5143820224719101</v>
+        <v>0.5181434599156118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1460470810544666</v>
+        <v>0.1468139188360067</v>
       </c>
       <c r="H3" t="n">
-        <v>0.317741935483871</v>
+        <v>0.3221629855293222</v>
       </c>
       <c r="I3" t="n">
-        <v>0.256629213483146</v>
+        <v>0.250210970464135</v>
       </c>
       <c r="J3" t="n">
-        <v>13.78125</v>
+        <v>13.79411764705882</v>
       </c>
       <c r="K3" t="n">
-        <v>11.6875</v>
+        <v>12.08823529411765</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5.794117647058823</v>
       </c>
       <c r="M3" t="n">
-        <v>12.65625</v>
+        <v>12.76470588235294</v>
       </c>
       <c r="N3" t="n">
-        <v>34.15625</v>
+        <v>33.85294117647059</v>
       </c>
       <c r="O3" t="n">
-        <v>47.125</v>
+        <v>46.79411764705883</v>
       </c>
       <c r="P3" t="n">
-        <v>0.677752808988764</v>
+        <v>0.6713080168776372</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.147058823529412</v>
       </c>
       <c r="R3" t="n">
-        <v>13.71875</v>
+        <v>13.61764705882353</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1973033707865169</v>
+        <v>0.1953586497890295</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53125</v>
+        <v>2.470588235294118</v>
       </c>
       <c r="U3" t="n">
-        <v>8.1875</v>
+        <v>8.088235294117647</v>
       </c>
       <c r="V3" t="n">
-        <v>0.117752808988764</v>
+        <v>0.1160337552742616</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59375</v>
+        <v>1.705882352941176</v>
       </c>
       <c r="X3" t="n">
-        <v>5.65625</v>
+        <v>5.852941176470588</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08134831460674158</v>
+        <v>0.0839662447257384</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.1875</v>
+        <v>6.352941176470588</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.125</v>
+        <v>19.11764705882353</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2750561797752809</v>
+        <v>0.2742616033755274</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7248010610079576</v>
+        <v>0.7234443746071653</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3826879271070615</v>
+        <v>0.3779697624190065</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3091603053435115</v>
+        <v>0.3054545454545455</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.281767955801105</v>
+        <v>0.2914572864321608</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3323076923076923</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.449602122015915</v>
+        <v>1.446888749214331</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6183206106870229</v>
+        <v>0.610909090909091</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9419924337957125</v>
+        <v>0.9681978798586572</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.857976653696498</v>
+        <v>0.8621323529411765</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.949238578680203</v>
+        <v>0.9716312056737588</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.655172413793103</v>
+        <v>1.669491525423729</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.291571753986333</v>
+        <v>1.29637526652452</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.068337129840547</v>
+        <v>5.053304904051172</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.359908883826879</v>
+        <v>6.349680170575693</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2590.36</v>
+        <v>2750.48</v>
       </c>
       <c r="C4" t="n">
-        <v>2601.12</v>
+        <v>2761</v>
       </c>
       <c r="D4" t="n">
-        <v>113.8355785200222</v>
+        <v>114.1615356754799</v>
       </c>
       <c r="E4" t="n">
-        <v>109.9526357876607</v>
+        <v>110.4310032596885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5614077669902913</v>
+        <v>0.5657352267521759</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1745117744520194</v>
+        <v>0.1743880390321464</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3212669683257919</v>
+        <v>0.3167381974248927</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3145631067961165</v>
+        <v>0.3124141090242785</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="M4" t="n">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="N4" t="n">
-        <v>1072</v>
+        <v>1142</v>
       </c>
       <c r="O4" t="n">
-        <v>1408</v>
+        <v>1496</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6834951456310679</v>
+        <v>0.6852954649564819</v>
       </c>
       <c r="Q4" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="R4" t="n">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1533980582524272</v>
+        <v>0.1516262024736601</v>
       </c>
       <c r="T4" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="U4" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1135922330097087</v>
+        <v>0.114063215758131</v>
       </c>
       <c r="W4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X4" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1077669902912621</v>
+        <v>0.1058176820888685</v>
       </c>
       <c r="Z4" t="n">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="AA4" t="n">
-        <v>724</v>
+        <v>768</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3514563106796116</v>
+        <v>0.3518094365551993</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7613636363636364</v>
+        <v>0.7633689839572193</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4493670886075949</v>
+        <v>0.4501510574018127</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3815261044176707</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4458874458874459</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.319060773480663</v>
+        <v>0.3268229166666667</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.522727272727273</v>
+        <v>1.526737967914439</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7630522088353414</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.056025369978858</v>
+        <v>1.063063063063063</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8041002277904328</v>
+        <v>0.8230277185501066</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.005633802816901</v>
+        <v>1.018970189701897</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.559701492537313</v>
+        <v>1.58273381294964</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.186770428015564</v>
+        <v>1.189338235294118</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.007782101167315</v>
+        <v>4.012867647058823</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.19455252918288</v>
+        <v>5.202205882352941</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.94875</v>
+        <v>80.89647058823529</v>
       </c>
       <c r="C5" t="n">
-        <v>81.285</v>
+        <v>81.20588235294116</v>
       </c>
       <c r="D5" t="n">
-        <v>113.8355785200222</v>
+        <v>114.1615356754799</v>
       </c>
       <c r="E5" t="n">
-        <v>109.9526357876607</v>
+        <v>110.4310032596886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5614077669902913</v>
+        <v>0.565735226752176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1745117744520194</v>
+        <v>0.1743880390321464</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3212669683257919</v>
+        <v>0.3167381974248927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3145631067961165</v>
+        <v>0.3124141090242785</v>
       </c>
       <c r="J5" t="n">
-        <v>11.03125</v>
+        <v>11.35294117647059</v>
       </c>
       <c r="K5" t="n">
-        <v>11.15625</v>
+        <v>11.05882352941176</v>
       </c>
       <c r="L5" t="n">
-        <v>6.53125</v>
+        <v>6.470588235294118</v>
       </c>
       <c r="M5" t="n">
-        <v>15.46875</v>
+        <v>15.44117647058824</v>
       </c>
       <c r="N5" t="n">
-        <v>33.5</v>
+        <v>33.58823529411764</v>
       </c>
       <c r="O5" t="n">
         <v>44</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6834951456310679</v>
+        <v>0.685295464956482</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4375</v>
+        <v>4.382352941176471</v>
       </c>
       <c r="R5" t="n">
-        <v>9.875</v>
+        <v>9.735294117647058</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1533980582524272</v>
+        <v>0.1516262024736601</v>
       </c>
       <c r="T5" t="n">
-        <v>2.84375</v>
+        <v>2.794117647058823</v>
       </c>
       <c r="U5" t="n">
-        <v>7.3125</v>
+        <v>7.323529411764706</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1135922330097087</v>
+        <v>0.114063215758131</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1875</v>
+        <v>3.029411764705882</v>
       </c>
       <c r="X5" t="n">
-        <v>6.9375</v>
+        <v>6.794117647058823</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1077669902912621</v>
+        <v>0.1058176820888685</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.21875</v>
+        <v>7.382352941176471</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.625</v>
+        <v>22.58823529411765</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3514563106796116</v>
+        <v>0.3518094365551993</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7613636363636364</v>
+        <v>0.7633689839572192</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4493670886075949</v>
+        <v>0.4501510574018128</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3815261044176707</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4458874458874459</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.319060773480663</v>
+        <v>0.3268229166666667</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.522727272727273</v>
+        <v>1.526737967914438</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7630522088353413</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.056025369978858</v>
+        <v>1.063063063063063</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8041002277904328</v>
+        <v>0.8230277185501066</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.005633802816901</v>
+        <v>1.018970189701897</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.559701492537313</v>
+        <v>1.58273381294964</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.186770428015564</v>
+        <v>1.189338235294118</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.007782101167315</v>
+        <v>4.012867647058823</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.19455252918288</v>
+        <v>5.202205882352941</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I8" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K8" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="S8" t="n">
+        <v>78</v>
+      </c>
+      <c r="T8" t="n">
+        <v>368</v>
+      </c>
+      <c r="U8" t="n">
         <v>75</v>
       </c>
-      <c r="T8" t="n">
-        <v>349</v>
-      </c>
-      <c r="U8" t="n">
-        <v>73</v>
-      </c>
       <c r="V8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W8" t="n">
         <v>29</v>
@@ -1488,84 +1488,84 @@
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="Z8" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC8" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.478</v>
+        <v>0.442</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.356</v>
+        <v>0.34</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>680:03</t>
+          <t>712:47</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>309.4</v>
+        <v>328.16</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.63</v>
+        <v>0.619</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.041</v>
+        <v>1.027</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.175</v>
+        <v>0.171</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.252</v>
+        <v>0.249</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.194</v>
+        <v>0.197</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.149</v>
+        <v>0.151</v>
       </c>
       <c r="AY8" t="n">
         <v>0.041</v>
@@ -1578,16 +1578,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1647,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1693,20 +1693,20 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>01:31</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.282</v>
+        <v>0.432</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.767</v>
+        <v>0.395</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>74</v>
+      </c>
+      <c r="D10" t="n">
         <v>31</v>
       </c>
-      <c r="C10" t="n">
-        <v>72</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30</v>
-      </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1761,37 +1761,37 @@
         <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
-        <v>14</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
       <c r="R10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="U10" t="n">
         <v>6</v>
@@ -1806,13 +1806,13 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.654</v>
+        <v>0.66</v>
       </c>
       <c r="AB10" t="n">
         <v>8</v>
@@ -1852,41 +1852,41 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>193:39</t>
+          <t>211:15</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>68.36</v>
+        <v>71.36</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.587</v>
+        <v>0.593</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.053</v>
+        <v>1.037</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.102</v>
+        <v>0.126</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.151</v>
+        <v>0.144</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="11">
@@ -2055,34 +2055,34 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -2097,22 +2097,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2124,13 +2124,13 @@
         <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.579</v>
+        <v>0.64</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2145,19 +2145,19 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AH12" t="n">
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
         <v>2</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>72:47</t>
+          <t>86:45</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>37.28</v>
+        <v>45.04</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.293</v>
+        <v>0.318</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.365</v>
+        <v>0.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.671</v>
+        <v>0.71</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.276</v>
+        <v>0.333</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="13">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H13" t="n">
         <v>37</v>
@@ -2238,43 +2238,43 @@
         <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="n">
         <v>49</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R13" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T13" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W13" t="n">
         <v>12</v>
@@ -2283,13 +2283,13 @@
         <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="AB13" t="n">
         <v>7</v>
@@ -2319,51 +2319,51 @@
         <v>0.286</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.269</v>
+        <v>0.273</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>584:24</t>
+          <t>608:15</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>184.12</v>
+        <v>191.12</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.392</v>
+        <v>0.399</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.462</v>
+        <v>0.466</v>
       </c>
       <c r="AR13" t="n">
         <v>0.733</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.206</v>
+        <v>0.215</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.296</v>
+        <v>0.287</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.395</v>
+        <v>2.244</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2397,16 +2397,16 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
@@ -2421,34 +2421,34 @@
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="U14" t="n">
         <v>9</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.769</v>
+        <v>0.733</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
@@ -2469,60 +2469,60 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AL14" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.364</v>
+        <v>0.448</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>221:30</t>
+          <t>261:25</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>51.76</v>
+        <v>62.76</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.533</v>
+        <v>0.607</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.535</v>
+        <v>0.606</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.966</v>
+        <v>1.115</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.097</v>
+        <v>0.08</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.094</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="15">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
         <v>41</v>
@@ -2547,7 +2547,7 @@
         <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2556,13 +2556,13 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M15" t="n">
         <v>19</v>
@@ -2580,13 +2580,13 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U15" t="n">
         <v>6</v>
@@ -2631,10 +2631,10 @@
         <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AK15" t="n">
         <v>3</v>
@@ -2647,41 +2647,41 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>265:54</t>
+          <t>279:33</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>46.76</v>
+        <v>48.76</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.453</v>
+        <v>0.433</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.458</v>
+        <v>0.438</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.877</v>
+        <v>0.841</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AV15" t="n">
         <v>0.075</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="16">
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="D16" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H16" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I16" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J16" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K16" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L16" t="n">
         <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S16" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="T16" t="n">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="U16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="V16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W16" t="n">
         <v>31</v>
@@ -2760,87 +2760,87 @@
         <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.778</v>
+        <v>0.77</v>
       </c>
       <c r="AB16" t="n">
         <v>23</v>
       </c>
       <c r="AC16" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.418</v>
+        <v>0.404</v>
       </c>
       <c r="AE16" t="n">
         <v>18</v>
       </c>
       <c r="AF16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.419</v>
+        <v>0.409</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.296</v>
+        <v>0.31</v>
       </c>
       <c r="AK16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.331</v>
+        <v>0.325</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>821:57</t>
+          <t>864:23</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>447.64</v>
+        <v>469.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.548</v>
+        <v>0.537</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.598</v>
+        <v>0.59</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.079</v>
+        <v>1.059</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.098</v>
+        <v>0.102</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.301</v>
+        <v>0.298</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.909</v>
+        <v>1.792</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.098</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="17">
@@ -2850,40 +2850,40 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>167</v>
+      </c>
+      <c r="D17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
         <v>21</v>
       </c>
-      <c r="C17" t="n">
-        <v>148</v>
-      </c>
-      <c r="D17" t="n">
-        <v>28</v>
-      </c>
-      <c r="E17" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26</v>
-      </c>
-      <c r="G17" t="n">
-        <v>82</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="n">
-        <v>17</v>
-      </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
         <v>5</v>
@@ -2892,25 +2892,25 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
+        <v>16</v>
+      </c>
+      <c r="S17" t="n">
         <v>14</v>
       </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
       <c r="T17" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="W17" t="n">
         <v>13</v>
@@ -2919,13 +2919,13 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.667</v>
+        <v>0.642</v>
       </c>
       <c r="AB17" t="n">
         <v>6</v>
@@ -2937,69 +2937,69 @@
         <v>0.545</v>
       </c>
       <c r="AE17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.571</v>
+        <v>0.474</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.269</v>
+        <v>0.271</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>397:18</t>
+          <t>444:35</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>152.48</v>
+        <v>174.24</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.971</v>
+        <v>0.958</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.538</v>
+        <v>1.533</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.164</v>
+        <v>0.167</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.146</v>
+        <v>0.158</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="18">
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3327,67 +3327,67 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I20" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J20" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K20" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="R20" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="S20" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="T20" t="n">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="U20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="V20" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="W20" t="n">
         <v>14</v>
@@ -3396,87 +3396,87 @@
         <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="Z20" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.3</v>
+        <v>0.309</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.455</v>
+        <v>0.441</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.397</v>
+        <v>0.418</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>571:31</t>
+          <t>621:18</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>312.76</v>
+        <v>343.72</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.502</v>
+        <v>0.518</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.93</v>
+        <v>0.948</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.283</v>
+        <v>0.289</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.192</v>
+        <v>2.085</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="AX20" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="21">
@@ -3632,7 +3632,7 @@
         <v>0.152</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.237</v>
+        <v>0.239</v>
       </c>
       <c r="AY21" t="n">
         <v>0.002</v>
@@ -3791,10 +3791,10 @@
         <v>0.068</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="23">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D23" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E23" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3825,46 +3825,46 @@
         <v>59</v>
       </c>
       <c r="I23" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J23" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L23" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M23" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R23" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T23" t="n">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="U23" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="V23" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="W23" t="n">
         <v>11</v>
@@ -3873,22 +3873,22 @@
         <v>7</v>
       </c>
       <c r="Y23" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Z23" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.742</v>
+        <v>0.728</v>
       </c>
       <c r="AB23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC23" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="AE23" t="n">
         <v>6</v>
@@ -3919,41 +3919,41 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>567:45</t>
+          <t>605:06</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>294.28</v>
+        <v>310.16</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.033</v>
+        <v>1.019</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.273</v>
+        <v>0.257</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.15</v>
+        <v>1.317</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.178</v>
+        <v>0.186</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="24">
@@ -4106,10 +4106,10 @@
         <v>0.138</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4122,91 +4122,91 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" t="n">
+        <v>55</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" t="n">
         <v>14</v>
       </c>
-      <c r="G25" t="n">
-        <v>38</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>8</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>19</v>
+      </c>
+      <c r="R25" t="n">
+        <v>25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>73</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC25" t="n">
         <v>5</v>
       </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>15</v>
-      </c>
-      <c r="R25" t="n">
-        <v>18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>11</v>
-      </c>
-      <c r="T25" t="n">
-        <v>43</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4</v>
-      </c>
       <c r="AD25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AE25" t="n">
         <v>2</v>
@@ -4218,60 +4218,60 @@
         <v>0.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.382</v>
+        <v>0.417</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>127:34</t>
+          <t>168:30</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>75.72</v>
+        <v>104.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.601</v>
+        <v>0.654</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.964</v>
+        <v>1.071</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.198</v>
+        <v>0.182</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.2</v>
+        <v>0.165</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.6</v>
+        <v>0.737</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.254</v>
+        <v>0.265</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="26">
@@ -4281,16 +4281,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4299,19 +4299,19 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I26" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L26" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
         <v>7</v>
@@ -4323,25 +4323,25 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="S26" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T26" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="U26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V26" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
@@ -4350,31 +4350,31 @@
         <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="Z26" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.667</v>
+        <v>0.679</v>
       </c>
       <c r="AB26" t="n">
         <v>24</v>
       </c>
       <c r="AC26" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.462</v>
+        <v>0.444</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -4396,41 +4396,41 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>453:21</t>
+          <t>478:25</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>207.48</v>
+        <v>219.36</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.588</v>
+        <v>0.591</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.012</v>
+        <v>1.021</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.295</v>
+        <v>0.289</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.655</v>
+        <v>0.7</v>
       </c>
       <c r="AV26" t="n">
         <v>0.196</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="27">
@@ -4589,7 +4589,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.066</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="28">
@@ -4599,22 +4599,22 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>13</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="E28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -4623,13 +4623,13 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -4641,25 +4641,25 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U28" t="n">
         <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
         <v>5</v>
@@ -4668,13 +4668,13 @@
         <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4689,19 +4689,19 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AK28" t="n">
         <v>1</v>
@@ -4714,41 +4714,41 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>43:32</t>
+          <t>57:36</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>15.44</v>
+        <v>20.44</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.4</v>
+        <v>0.447</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.421</v>
+        <v>0.463</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.842</v>
+        <v>0.881</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.067</v>
+        <v>0.053</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>0.152</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="29">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L29" t="n">
         <v>48</v>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -4917,144 +4917,144 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>2860</v>
+        <v>3049</v>
       </c>
       <c r="D30" t="n">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="E30" t="n">
-        <v>1432</v>
+        <v>1521</v>
       </c>
       <c r="F30" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="G30" t="n">
-        <v>793</v>
+        <v>849</v>
       </c>
       <c r="H30" t="n">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="I30" t="n">
-        <v>777</v>
+        <v>808</v>
       </c>
       <c r="J30" t="n">
-        <v>567</v>
+        <v>608</v>
       </c>
       <c r="K30" t="n">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="L30" t="n">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="M30" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="N30" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="Q30" t="n">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="R30" t="n">
-        <v>769</v>
+        <v>818</v>
       </c>
       <c r="S30" t="n">
-        <v>736</v>
+        <v>773</v>
       </c>
       <c r="T30" t="n">
-        <v>3197</v>
+        <v>3405</v>
       </c>
       <c r="U30" t="n">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="V30" t="n">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="W30" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="X30" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y30" t="n">
-        <v>1093</v>
+        <v>1151</v>
       </c>
       <c r="Z30" t="n">
-        <v>1508</v>
+        <v>1591</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="AB30" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AC30" t="n">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.383</v>
+        <v>0.378</v>
       </c>
       <c r="AE30" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AF30" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="AH30" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AI30" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.282</v>
+        <v>0.291</v>
       </c>
       <c r="AK30" t="n">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="AL30" t="n">
-        <v>612</v>
+        <v>650</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.324</v>
+        <v>0.332</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>3005.88</v>
+        <v>3194.52</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.514</v>
+        <v>0.518</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.257</v>
+        <v>0.25</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.292</v>
+        <v>1.296</v>
       </c>
       <c r="AV30" t="n">
         <v>0.2</v>
@@ -5063,7 +5063,7 @@
         <v>0.064</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.136</v>
+        <v>0.137</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5076,150 +5076,150 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>2961</v>
+        <v>3152</v>
       </c>
       <c r="D31" t="n">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="E31" t="n">
-        <v>1114</v>
+        <v>1184</v>
       </c>
       <c r="F31" t="n">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="G31" t="n">
-        <v>946</v>
+        <v>999</v>
       </c>
       <c r="H31" t="n">
-        <v>648</v>
+        <v>682</v>
       </c>
       <c r="I31" t="n">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="J31" t="n">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="K31" t="n">
-        <v>846</v>
+        <v>890</v>
       </c>
       <c r="L31" t="n">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="M31" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="N31" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="Q31" t="n">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="R31" t="n">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="S31" t="n">
-        <v>766</v>
+        <v>815</v>
       </c>
       <c r="T31" t="n">
-        <v>3428</v>
+        <v>3656</v>
       </c>
       <c r="U31" t="n">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="V31" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="W31" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="X31" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="Y31" t="n">
-        <v>1072</v>
+        <v>1142</v>
       </c>
       <c r="Z31" t="n">
-        <v>1408</v>
+        <v>1496</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="AB31" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AC31" t="n">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AF31" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.389</v>
+        <v>0.382</v>
       </c>
       <c r="AH31" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AI31" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.459</v>
+        <v>0.446</v>
       </c>
       <c r="AK31" t="n">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="AL31" t="n">
-        <v>724</v>
+        <v>768</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.319</v>
+        <v>0.327</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2945.36</v>
+        <v>3119.48</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.609</v>
+        <v>0.612</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.005</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.315</v>
+        <v>0.312</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.187</v>
+        <v>1.189</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="AX31" t="n">
         <v>0.136</v>
@@ -5292,153 +5292,153 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>10.062</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>3.281</v>
+        <v>3.265</v>
       </c>
       <c r="E33" t="n">
-        <v>4.938</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>1.875</v>
+        <v>1.853</v>
       </c>
       <c r="H33" t="n">
-        <v>1.719</v>
+        <v>1.706</v>
       </c>
       <c r="I33" t="n">
-        <v>2.656</v>
+        <v>2.618</v>
       </c>
       <c r="J33" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="K33" t="n">
-        <v>2.719</v>
+        <v>2.706</v>
       </c>
       <c r="L33" t="n">
-        <v>1.188</v>
+        <v>1.324</v>
       </c>
       <c r="M33" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="N33" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.688</v>
+        <v>1.647</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.688</v>
+        <v>1.647</v>
       </c>
       <c r="R33" t="n">
-        <v>2.469</v>
+        <v>2.441</v>
       </c>
       <c r="S33" t="n">
-        <v>2.344</v>
+        <v>2.294</v>
       </c>
       <c r="T33" t="n">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="U33" t="n">
-        <v>2.281</v>
+        <v>2.206</v>
       </c>
       <c r="V33" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="W33" t="n">
-        <v>0.906</v>
+        <v>0.853</v>
       </c>
       <c r="X33" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="Y33" t="n">
-        <v>4.188</v>
+        <v>4.118</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.656</v>
+        <v>5.559</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.438</v>
+        <v>1.529</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.478</v>
+        <v>0.442</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.125</v>
+        <v>0.176</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.406</v>
+        <v>1.382</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.356</v>
+        <v>0.34</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.669</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.63</v>
+        <v>0.619</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.041</v>
+        <v>1.027</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.175</v>
+        <v>0.171</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.252</v>
+        <v>0.249</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.194</v>
+        <v>0.197</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.149</v>
+        <v>0.151</v>
       </c>
       <c r="AY33" t="n">
         <v>0.041</v>
@@ -5451,22 +5451,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5499,13 +5499,13 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5520,13 +5520,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -5559,27 +5559,27 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>00:59</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
@@ -5591,13 +5591,13 @@
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.282</v>
+        <v>0.432</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.767</v>
+        <v>0.395</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -5610,88 +5610,88 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>2.323</v>
+        <v>2.242</v>
       </c>
       <c r="D35" t="n">
-        <v>0.968</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>1.645</v>
+        <v>1.576</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="H35" t="n">
-        <v>0.387</v>
+        <v>0.364</v>
       </c>
       <c r="I35" t="n">
-        <v>0.613</v>
+        <v>0.576</v>
       </c>
       <c r="J35" t="n">
-        <v>0.161</v>
+        <v>0.212</v>
       </c>
       <c r="K35" t="n">
-        <v>0.742</v>
+        <v>0.788</v>
       </c>
       <c r="L35" t="n">
-        <v>0.29</v>
+        <v>0.303</v>
       </c>
       <c r="M35" t="n">
-        <v>0.29</v>
+        <v>0.303</v>
       </c>
       <c r="N35" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.226</v>
+        <v>0.273</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.226</v>
+        <v>0.273</v>
       </c>
       <c r="R35" t="n">
-        <v>1.452</v>
+        <v>1.424</v>
       </c>
       <c r="S35" t="n">
-        <v>0.355</v>
+        <v>0.364</v>
       </c>
       <c r="T35" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="U35" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="V35" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="W35" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="X35" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.097</v>
+        <v>1.061</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.677</v>
+        <v>1.606</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.654</v>
+        <v>0.66</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="AD35" t="n">
         <v>0.571</v>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5718,48 +5718,48 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>2.205</v>
+        <v>2.162</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.587</v>
+        <v>0.593</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.053</v>
+        <v>1.037</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.102</v>
+        <v>0.126</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.151</v>
+        <v>0.144</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="36">
@@ -5928,40 +5928,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>4.167</v>
+        <v>4.571</v>
       </c>
       <c r="D37" t="n">
-        <v>0.667</v>
+        <v>0.857</v>
       </c>
       <c r="E37" t="n">
-        <v>2.667</v>
+        <v>2.714</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="G37" t="n">
-        <v>2.167</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1.333</v>
+        <v>1.571</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.286</v>
       </c>
       <c r="J37" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="K37" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="L37" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="M37" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5970,114 +5970,114 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="R37" t="n">
-        <v>1.667</v>
+        <v>2.143</v>
       </c>
       <c r="S37" t="n">
-        <v>1.833</v>
+        <v>1.857</v>
       </c>
       <c r="T37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="X37" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.833</v>
+        <v>2.286</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.167</v>
+        <v>3.571</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.579</v>
+        <v>0.64</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.667</v>
+        <v>1.429</v>
       </c>
       <c r="AM37" t="n">
         <v>0.2</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.213</v>
+        <v>6.434</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.293</v>
+        <v>0.318</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.365</v>
+        <v>0.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.671</v>
+        <v>0.71</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.276</v>
+        <v>0.333</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="38">
@@ -6087,88 +6087,88 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C38" t="n">
-        <v>4.821</v>
+        <v>4.667</v>
       </c>
       <c r="D38" t="n">
-        <v>0.786</v>
+        <v>0.767</v>
       </c>
       <c r="E38" t="n">
-        <v>2.107</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.643</v>
+        <v>0.633</v>
       </c>
       <c r="G38" t="n">
-        <v>2.357</v>
+        <v>2.3</v>
       </c>
       <c r="H38" t="n">
-        <v>1.321</v>
+        <v>1.233</v>
       </c>
       <c r="I38" t="n">
-        <v>1.714</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.067</v>
       </c>
       <c r="K38" t="n">
-        <v>1.75</v>
+        <v>1.633</v>
       </c>
       <c r="L38" t="n">
-        <v>0.357</v>
+        <v>0.4</v>
       </c>
       <c r="M38" t="n">
-        <v>1.071</v>
+        <v>1.067</v>
       </c>
       <c r="N38" t="n">
-        <v>0.179</v>
+        <v>0.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.357</v>
+        <v>1.367</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.357</v>
+        <v>1.367</v>
       </c>
       <c r="R38" t="n">
-        <v>2.821</v>
+        <v>2.7</v>
       </c>
       <c r="S38" t="n">
-        <v>2.143</v>
+        <v>2.067</v>
       </c>
       <c r="T38" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="U38" t="n">
-        <v>0.607</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V38" t="n">
-        <v>0.464</v>
+        <v>0.533</v>
       </c>
       <c r="W38" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="X38" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.857</v>
+        <v>1.767</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.464</v>
+        <v>2.333</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.107</v>
+        <v>1.033</v>
       </c>
       <c r="AD38" t="n">
         <v>0.226</v>
@@ -6177,16 +6177,16 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AJ38" t="n">
         <v>0.286</v>
@@ -6195,48 +6195,48 @@
         <v>0.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.857</v>
+        <v>1.833</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.269</v>
+        <v>0.273</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>6.576</v>
+        <v>6.371</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.392</v>
+        <v>0.399</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.462</v>
+        <v>0.466</v>
       </c>
       <c r="AR38" t="n">
         <v>0.733</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.206</v>
+        <v>0.215</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.296</v>
+        <v>0.287</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.395</v>
+        <v>2.244</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -6246,88 +6246,88 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>1.667</v>
+        <v>2.188</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3</v>
+        <v>0.312</v>
       </c>
       <c r="E39" t="n">
-        <v>0.433</v>
+        <v>0.469</v>
       </c>
       <c r="F39" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.067</v>
+        <v>1.281</v>
       </c>
       <c r="H39" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="I39" t="n">
-        <v>0.133</v>
+        <v>0.125</v>
       </c>
       <c r="J39" t="n">
-        <v>0.067</v>
+        <v>0.125</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="L39" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="M39" t="n">
-        <v>0.267</v>
+        <v>0.312</v>
       </c>
       <c r="N39" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="R39" t="n">
-        <v>1.033</v>
+        <v>1.156</v>
       </c>
       <c r="S39" t="n">
-        <v>0.167</v>
+        <v>0.188</v>
       </c>
       <c r="T39" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="V39" t="n">
-        <v>0.433</v>
+        <v>0.594</v>
       </c>
       <c r="W39" t="n">
-        <v>0.1</v>
+        <v>0.188</v>
       </c>
       <c r="X39" t="n">
-        <v>0.033</v>
+        <v>0.062</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.333</v>
+        <v>0.344</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.433</v>
+        <v>0.469</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.769</v>
+        <v>0.733</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="AD39" t="n">
         <v>0.333</v>
@@ -6336,66 +6336,66 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.067</v>
+        <v>0.094</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.267</v>
+        <v>0.406</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.733</v>
+        <v>0.906</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.364</v>
+        <v>0.448</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1.725</v>
+        <v>1.961</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.533</v>
+        <v>0.607</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.535</v>
+        <v>0.606</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.966</v>
+        <v>1.115</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.097</v>
+        <v>0.08</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.094</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>1.367</v>
+        <v>1.323</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E40" t="n">
-        <v>0.533</v>
+        <v>0.516</v>
       </c>
       <c r="F40" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="I40" t="n">
-        <v>0.133</v>
+        <v>0.129</v>
       </c>
       <c r="J40" t="n">
-        <v>0.167</v>
+        <v>0.194</v>
       </c>
       <c r="K40" t="n">
-        <v>0.367</v>
+        <v>0.419</v>
       </c>
       <c r="L40" t="n">
-        <v>0.533</v>
+        <v>0.548</v>
       </c>
       <c r="M40" t="n">
-        <v>0.633</v>
+        <v>0.613</v>
       </c>
       <c r="N40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>1.258</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="T40" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="V40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="W40" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="X40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AA40" t="n">
         <v>0.667</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.133</v>
+        <v>0.129</v>
       </c>
       <c r="AD40" t="n">
         <v>0.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="AG40" t="n">
         <v>0.429</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.133</v>
+        <v>0.129</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.533</v>
+        <v>0.581</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AM40" t="n">
         <v>0.273</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>1.559</v>
+        <v>1.573</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.453</v>
+        <v>0.433</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.458</v>
+        <v>0.438</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.877</v>
+        <v>0.841</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AV40" t="n">
         <v>0.075</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="41">
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C41" t="n">
-        <v>15.581</v>
+        <v>15.061</v>
       </c>
       <c r="D41" t="n">
-        <v>3.839</v>
+        <v>3.667</v>
       </c>
       <c r="E41" t="n">
-        <v>6.484</v>
+        <v>6.364</v>
       </c>
       <c r="F41" t="n">
-        <v>1.516</v>
+        <v>1.485</v>
       </c>
       <c r="G41" t="n">
-        <v>4.677</v>
+        <v>4.606</v>
       </c>
       <c r="H41" t="n">
-        <v>3.355</v>
+        <v>3.273</v>
       </c>
       <c r="I41" t="n">
-        <v>4.226</v>
+        <v>4.091</v>
       </c>
       <c r="J41" t="n">
-        <v>2.71</v>
+        <v>2.606</v>
       </c>
       <c r="K41" t="n">
-        <v>2.226</v>
+        <v>2.303</v>
       </c>
       <c r="L41" t="n">
-        <v>0.903</v>
+        <v>0.848</v>
       </c>
       <c r="M41" t="n">
-        <v>1.516</v>
+        <v>1.455</v>
       </c>
       <c r="N41" t="n">
-        <v>0.613</v>
+        <v>0.667</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.419</v>
+        <v>1.455</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.419</v>
+        <v>1.455</v>
       </c>
       <c r="R41" t="n">
-        <v>1.516</v>
+        <v>1.485</v>
       </c>
       <c r="S41" t="n">
-        <v>3.71</v>
+        <v>3.636</v>
       </c>
       <c r="T41" t="n">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="U41" t="n">
-        <v>2.29</v>
+        <v>2.212</v>
       </c>
       <c r="V41" t="n">
-        <v>1.419</v>
+        <v>1.394</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>0.613</v>
+        <v>0.576</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.871</v>
+        <v>5.697</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.548</v>
+        <v>7.394</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.778</v>
+        <v>0.77</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.742</v>
+        <v>0.697</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.774</v>
+        <v>1.727</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.418</v>
+        <v>0.404</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.387</v>
+        <v>1.333</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.419</v>
+        <v>0.409</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.258</v>
+        <v>0.273</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.871</v>
+        <v>0.879</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.296</v>
+        <v>0.31</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.258</v>
+        <v>1.212</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.806</v>
+        <v>3.727</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.331</v>
+        <v>0.325</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>26:30</t>
+          <t>26:11</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>14.44</v>
+        <v>14.224</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.548</v>
+        <v>0.537</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.598</v>
+        <v>0.59</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.079</v>
+        <v>1.059</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.098</v>
+        <v>0.102</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.301</v>
+        <v>0.298</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.909</v>
+        <v>1.792</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.102</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="42">
@@ -6723,156 +6723,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C42" t="n">
-        <v>7.048</v>
+        <v>7.261</v>
       </c>
       <c r="D42" t="n">
-        <v>1.333</v>
+        <v>1.478</v>
       </c>
       <c r="E42" t="n">
-        <v>2.381</v>
+        <v>2.696</v>
       </c>
       <c r="F42" t="n">
-        <v>1.238</v>
+        <v>1.217</v>
       </c>
       <c r="G42" t="n">
-        <v>3.905</v>
+        <v>3.826</v>
       </c>
       <c r="H42" t="n">
-        <v>0.667</v>
+        <v>0.652</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="J42" t="n">
-        <v>0.952</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>2.381</v>
+        <v>2.609</v>
       </c>
       <c r="L42" t="n">
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="M42" t="n">
-        <v>0.286</v>
+        <v>0.391</v>
       </c>
       <c r="N42" t="n">
-        <v>0.238</v>
+        <v>0.217</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.619</v>
+        <v>0.652</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.619</v>
+        <v>0.652</v>
       </c>
       <c r="R42" t="n">
-        <v>0.667</v>
+        <v>0.696</v>
       </c>
       <c r="S42" t="n">
-        <v>0.524</v>
+        <v>0.609</v>
       </c>
       <c r="T42" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="U42" t="n">
-        <v>1.095</v>
+        <v>1.174</v>
       </c>
       <c r="V42" t="n">
-        <v>0.952</v>
+        <v>1.043</v>
       </c>
       <c r="W42" t="n">
-        <v>0.619</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X42" t="n">
-        <v>0.238</v>
+        <v>0.217</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.333</v>
+        <v>1.478</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>2.304</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.667</v>
+        <v>0.642</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.286</v>
+        <v>0.261</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.524</v>
+        <v>0.478</v>
       </c>
       <c r="AD42" t="n">
         <v>0.545</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.381</v>
+        <v>0.391</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.667</v>
+        <v>0.826</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.571</v>
+        <v>0.474</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.381</v>
+        <v>0.391</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.714</v>
+        <v>0.783</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.857</v>
+        <v>0.826</v>
       </c>
       <c r="AL42" t="n">
-        <v>3.19</v>
+        <v>3.043</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.269</v>
+        <v>0.271</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>7.261</v>
+        <v>7.576</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.971</v>
+        <v>0.958</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.538</v>
+        <v>1.533</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.164</v>
+        <v>0.167</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.146</v>
+        <v>0.158</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="43">
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -7200,156 +7200,156 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>10.034</v>
+        <v>10.516</v>
       </c>
       <c r="D45" t="n">
-        <v>2.414</v>
+        <v>2.516</v>
       </c>
       <c r="E45" t="n">
-        <v>5.207</v>
+        <v>5.323</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>1.065</v>
       </c>
       <c r="G45" t="n">
-        <v>2.586</v>
+        <v>2.613</v>
       </c>
       <c r="H45" t="n">
-        <v>2.207</v>
+        <v>2.29</v>
       </c>
       <c r="I45" t="n">
-        <v>2.724</v>
+        <v>2.839</v>
       </c>
       <c r="J45" t="n">
-        <v>3.931</v>
+        <v>3.968</v>
       </c>
       <c r="K45" t="n">
-        <v>1.483</v>
+        <v>1.484</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="M45" t="n">
-        <v>1.414</v>
+        <v>1.355</v>
       </c>
       <c r="N45" t="n">
-        <v>0.379</v>
+        <v>0.387</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.793</v>
+        <v>1.903</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.793</v>
+        <v>1.903</v>
       </c>
       <c r="R45" t="n">
-        <v>2.621</v>
+        <v>2.613</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.258</v>
       </c>
       <c r="T45" t="n">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="U45" t="n">
-        <v>0.862</v>
+        <v>1.032</v>
       </c>
       <c r="V45" t="n">
-        <v>1.276</v>
+        <v>1.419</v>
       </c>
       <c r="W45" t="n">
-        <v>0.483</v>
+        <v>0.452</v>
       </c>
       <c r="X45" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.586</v>
+        <v>3.774</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.069</v>
+        <v>5.29</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.517</v>
+        <v>0.548</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.724</v>
+        <v>1.774</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.3</v>
+        <v>0.309</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.517</v>
+        <v>0.484</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.138</v>
+        <v>1.097</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.455</v>
+        <v>0.441</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.138</v>
+        <v>0.161</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.414</v>
+        <v>0.452</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.862</v>
+        <v>0.903</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.172</v>
+        <v>2.161</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.397</v>
+        <v>0.418</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>10.785</v>
+        <v>11.088</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.502</v>
+        <v>0.518</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.93</v>
+        <v>0.948</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.283</v>
+        <v>0.289</v>
       </c>
       <c r="AU45" t="n">
-        <v>2.192</v>
+        <v>2.085</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="AX45" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.138</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="46">
@@ -7505,7 +7505,7 @@
         <v>0.152</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.237</v>
+        <v>0.239</v>
       </c>
       <c r="AY46" t="n">
         <v>0.007</v>
@@ -7664,10 +7664,10 @@
         <v>0.068</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="48">
@@ -7677,97 +7677,97 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C48" t="n">
-        <v>13.217</v>
+        <v>12.64</v>
       </c>
       <c r="D48" t="n">
-        <v>5.261</v>
+        <v>5.08</v>
       </c>
       <c r="E48" t="n">
-        <v>9.260999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F48" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="G48" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H48" t="n">
-        <v>2.565</v>
+        <v>2.36</v>
       </c>
       <c r="I48" t="n">
-        <v>3.783</v>
+        <v>3.56</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="K48" t="n">
-        <v>3.783</v>
+        <v>3.84</v>
       </c>
       <c r="L48" t="n">
-        <v>2.609</v>
+        <v>2.68</v>
       </c>
       <c r="M48" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="N48" t="n">
-        <v>1.391</v>
+        <v>1.32</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.739</v>
+        <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.739</v>
+        <v>1.64</v>
       </c>
       <c r="R48" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="S48" t="n">
-        <v>3.696</v>
+        <v>3.44</v>
       </c>
       <c r="T48" t="n">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="U48" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V48" t="n">
-        <v>2.826</v>
+        <v>2.76</v>
       </c>
       <c r="W48" t="n">
-        <v>0.478</v>
+        <v>0.44</v>
       </c>
       <c r="X48" t="n">
-        <v>0.304</v>
+        <v>0.28</v>
       </c>
       <c r="Y48" t="n">
-        <v>6.739</v>
+        <v>6.32</v>
       </c>
       <c r="Z48" t="n">
-        <v>9.087</v>
+        <v>8.68</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.742</v>
+        <v>0.728</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.826</v>
+        <v>0.88</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.522</v>
+        <v>2.64</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.261</v>
+        <v>0.24</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.435</v>
+        <v>1.32</v>
       </c>
       <c r="AG48" t="n">
         <v>0.182</v>
@@ -7782,51 +7782,51 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AM48" t="n">
         <v>0.333</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>24:41</t>
+          <t>24:12</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>12.795</v>
+        <v>12.406</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.033</v>
+        <v>1.019</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.273</v>
+        <v>0.257</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.15</v>
+        <v>1.317</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.178</v>
+        <v>0.186</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="49">
@@ -7979,10 +7979,10 @@
         <v>0.138</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,64 +7995,64 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>10.429</v>
+        <v>12.444</v>
       </c>
       <c r="D50" t="n">
-        <v>1.429</v>
+        <v>1.667</v>
       </c>
       <c r="E50" t="n">
-        <v>2.429</v>
+        <v>2.667</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>2.556</v>
       </c>
       <c r="G50" t="n">
-        <v>5.429</v>
+        <v>6.111</v>
       </c>
       <c r="H50" t="n">
-        <v>1.571</v>
+        <v>1.444</v>
       </c>
       <c r="I50" t="n">
-        <v>1.857</v>
+        <v>1.667</v>
       </c>
       <c r="J50" t="n">
-        <v>1.286</v>
+        <v>1.556</v>
       </c>
       <c r="K50" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="M50" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="N50" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.143</v>
+        <v>2.111</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.143</v>
+        <v>2.111</v>
       </c>
       <c r="R50" t="n">
-        <v>2.571</v>
+        <v>2.778</v>
       </c>
       <c r="S50" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="T50" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="U50" t="n">
-        <v>0.429</v>
+        <v>0.889</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -8061,90 +8061,90 @@
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.286</v>
+        <v>2.444</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>3.222</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.762</v>
+        <v>0.759</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="AG50" t="n">
         <v>0.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.571</v>
+        <v>0.778</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.857</v>
+        <v>2.222</v>
       </c>
       <c r="AL50" t="n">
-        <v>4.857</v>
+        <v>5.333</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.382</v>
+        <v>0.417</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>10.817</v>
+        <v>11.622</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.601</v>
+        <v>0.654</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.964</v>
+        <v>1.071</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.198</v>
+        <v>0.182</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.2</v>
+        <v>0.165</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.6</v>
+        <v>0.737</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.254</v>
+        <v>0.265</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="51">
@@ -8154,16 +8154,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C51" t="n">
-        <v>7.5</v>
+        <v>7.467</v>
       </c>
       <c r="D51" t="n">
-        <v>2.964</v>
+        <v>2.967</v>
       </c>
       <c r="E51" t="n">
-        <v>5.321</v>
+        <v>5.3</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -8172,82 +8172,82 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.571</v>
+        <v>1.533</v>
       </c>
       <c r="I51" t="n">
-        <v>2.393</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="T51" t="n">
+        <v>235</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0.679</v>
       </c>
-      <c r="K51" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.464</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.893</v>
-      </c>
-      <c r="T51" t="n">
-        <v>221</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>3.571</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>5.357</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AB51" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.857</v>
+        <v>1.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.462</v>
+        <v>0.444</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AF51" t="n">
         <v>0.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AH51" t="n">
         <v>0</v>
@@ -8269,41 +8269,41 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>7.41</v>
+        <v>7.312</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.588</v>
+        <v>0.591</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.012</v>
+        <v>1.021</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.295</v>
+        <v>0.289</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.655</v>
+        <v>0.7</v>
       </c>
       <c r="AV51" t="n">
         <v>0.196</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="52">
@@ -8462,7 +8462,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="53">
@@ -8472,88 +8472,88 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="D53" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G53" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="M53" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R53" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S53" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U53" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V53" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Y53" t="n">
         <v>1</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -8562,66 +8562,66 @@
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AJ53" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AK53" t="n">
         <v>0.2</v>
       </c>
-      <c r="AK53" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AL53" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AM53" t="n">
         <v>0.5</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>3.86</v>
+        <v>4.088</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.4</v>
+        <v>0.447</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.421</v>
+        <v>0.463</v>
       </c>
       <c r="AR53" t="n">
-        <v>0.842</v>
+        <v>0.881</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.067</v>
+        <v>0.053</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV53" t="n">
         <v>0.152</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX53" t="n">
         <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>0.016</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="54">
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -8658,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2.094</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>1.5</v>
+        <v>1.412</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -8673,13 +8673,13 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -8790,144 +8790,144 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C55" t="n">
-        <v>89.375</v>
+        <v>89.676</v>
       </c>
       <c r="D55" t="n">
-        <v>24.094</v>
+        <v>24.029</v>
       </c>
       <c r="E55" t="n">
-        <v>44.75</v>
+        <v>44.735</v>
       </c>
       <c r="F55" t="n">
-        <v>7.781</v>
+        <v>8.058999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>24.781</v>
+        <v>24.971</v>
       </c>
       <c r="H55" t="n">
-        <v>17.844</v>
+        <v>17.441</v>
       </c>
       <c r="I55" t="n">
-        <v>24.281</v>
+        <v>23.765</v>
       </c>
       <c r="J55" t="n">
-        <v>17.719</v>
+        <v>17.882</v>
       </c>
       <c r="K55" t="n">
-        <v>23.438</v>
+        <v>23.412</v>
       </c>
       <c r="L55" t="n">
-        <v>12.312</v>
+        <v>12.441</v>
       </c>
       <c r="M55" t="n">
-        <v>10.25</v>
+        <v>10.176</v>
       </c>
       <c r="N55" t="n">
-        <v>5.656</v>
+        <v>5.618</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>13.719</v>
+        <v>13.794</v>
       </c>
       <c r="Q55" t="n">
-        <v>12.656</v>
+        <v>12.765</v>
       </c>
       <c r="R55" t="n">
-        <v>24.031</v>
+        <v>24.059</v>
       </c>
       <c r="S55" t="n">
-        <v>23</v>
+        <v>22.735</v>
       </c>
       <c r="T55" t="n">
-        <v>3197</v>
+        <v>3405</v>
       </c>
       <c r="U55" t="n">
-        <v>13.781</v>
+        <v>13.794</v>
       </c>
       <c r="V55" t="n">
-        <v>11.688</v>
+        <v>12.088</v>
       </c>
       <c r="W55" t="n">
-        <v>6</v>
+        <v>5.794</v>
       </c>
       <c r="X55" t="n">
-        <v>3.625</v>
+        <v>3.471</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.156</v>
+        <v>33.853</v>
       </c>
       <c r="Z55" t="n">
-        <v>47.125</v>
+        <v>46.794</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="AB55" t="n">
-        <v>5.25</v>
+        <v>5.147</v>
       </c>
       <c r="AC55" t="n">
-        <v>13.719</v>
+        <v>13.618</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.383</v>
+        <v>0.378</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.531</v>
+        <v>2.471</v>
       </c>
       <c r="AF55" t="n">
-        <v>8.188000000000001</v>
+        <v>8.087999999999999</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.594</v>
+        <v>1.706</v>
       </c>
       <c r="AI55" t="n">
-        <v>5.656</v>
+        <v>5.853</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.282</v>
+        <v>0.291</v>
       </c>
       <c r="AK55" t="n">
-        <v>6.188</v>
+        <v>6.353</v>
       </c>
       <c r="AL55" t="n">
-        <v>19.125</v>
+        <v>19.118</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.324</v>
+        <v>0.332</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>93.934</v>
+        <v>93.956</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.514</v>
+        <v>0.518</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR55" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.257</v>
+        <v>0.25</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.292</v>
+        <v>1.296</v>
       </c>
       <c r="AV55" t="n">
         <v>0.2</v>
@@ -8936,7 +8936,7 @@
         <v>0.064</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.136</v>
+        <v>0.137</v>
       </c>
       <c r="AY55" t="n">
         <v>0</v>
@@ -8949,150 +8949,150 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" t="n">
-        <v>92.53100000000001</v>
+        <v>92.706</v>
       </c>
       <c r="D56" t="n">
-        <v>20.531</v>
+        <v>20.706</v>
       </c>
       <c r="E56" t="n">
-        <v>34.812</v>
+        <v>34.824</v>
       </c>
       <c r="F56" t="n">
-        <v>10.406</v>
+        <v>10.412</v>
       </c>
       <c r="G56" t="n">
-        <v>29.562</v>
+        <v>29.382</v>
       </c>
       <c r="H56" t="n">
-        <v>20.25</v>
+        <v>20.059</v>
       </c>
       <c r="I56" t="n">
-        <v>26.375</v>
+        <v>26.235</v>
       </c>
       <c r="J56" t="n">
-        <v>19.062</v>
+        <v>19.029</v>
       </c>
       <c r="K56" t="n">
-        <v>26.438</v>
+        <v>26.176</v>
       </c>
       <c r="L56" t="n">
-        <v>11.094</v>
+        <v>10.853</v>
       </c>
       <c r="M56" t="n">
-        <v>7.094</v>
+        <v>7.265</v>
       </c>
       <c r="N56" t="n">
-        <v>5.656</v>
+        <v>5.588</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>16.062</v>
+        <v>16</v>
       </c>
       <c r="Q56" t="n">
-        <v>15.469</v>
+        <v>15.441</v>
       </c>
       <c r="R56" t="n">
-        <v>23.062</v>
+        <v>22.794</v>
       </c>
       <c r="S56" t="n">
-        <v>23.938</v>
+        <v>23.971</v>
       </c>
       <c r="T56" t="n">
-        <v>3428</v>
+        <v>3656</v>
       </c>
       <c r="U56" t="n">
-        <v>11.031</v>
+        <v>11.353</v>
       </c>
       <c r="V56" t="n">
-        <v>11.156</v>
+        <v>11.059</v>
       </c>
       <c r="W56" t="n">
-        <v>6.531</v>
+        <v>6.471</v>
       </c>
       <c r="X56" t="n">
-        <v>4.188</v>
+        <v>4.088</v>
       </c>
       <c r="Y56" t="n">
-        <v>33.5</v>
+        <v>33.588</v>
       </c>
       <c r="Z56" t="n">
         <v>44</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.438</v>
+        <v>4.382</v>
       </c>
       <c r="AC56" t="n">
-        <v>9.875</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.844</v>
+        <v>2.794</v>
       </c>
       <c r="AF56" t="n">
-        <v>7.312</v>
+        <v>7.324</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.389</v>
+        <v>0.382</v>
       </c>
       <c r="AH56" t="n">
-        <v>3.188</v>
+        <v>3.029</v>
       </c>
       <c r="AI56" t="n">
-        <v>6.938</v>
+        <v>6.794</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.459</v>
+        <v>0.446</v>
       </c>
       <c r="AK56" t="n">
-        <v>7.219</v>
+        <v>7.382</v>
       </c>
       <c r="AL56" t="n">
-        <v>22.625</v>
+        <v>22.588</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.319</v>
+        <v>0.327</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>92.04300000000001</v>
+        <v>91.749</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.609</v>
+        <v>0.612</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.005</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.315</v>
+        <v>0.312</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.187</v>
+        <v>1.189</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="AX56" t="n">
         <v>0.153</v>
